--- a/results/mean_time_tables_sw.xlsx
+++ b/results/mean_time_tables_sw.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maciek\Documents\GitHub\UnlearningDataStreamPlayground\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{637DF0E7-EBA5-4FEF-B30F-70540205B4E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6840" yWindow="4755" windowWidth="28800" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="lr_0.0001" sheetId="1" r:id="rId1"/>
@@ -23,13 +17,28 @@
     <sheet name="lr_0.0008" sheetId="8" r:id="rId8"/>
     <sheet name="lr_0.0009" sheetId="9" r:id="rId9"/>
     <sheet name="lr_0.001" sheetId="10" r:id="rId10"/>
+    <sheet name="lr_0.0011" sheetId="11" r:id="rId11"/>
+    <sheet name="lr_0.0012" sheetId="12" r:id="rId12"/>
+    <sheet name="lr_0.0013" sheetId="13" r:id="rId13"/>
+    <sheet name="lr_0.0014" sheetId="14" r:id="rId14"/>
+    <sheet name="lr_0.0015" sheetId="15" r:id="rId15"/>
+    <sheet name="lr_0.0016" sheetId="16" r:id="rId16"/>
+    <sheet name="lr_0.0017" sheetId="17" r:id="rId17"/>
+    <sheet name="lr_0.0018" sheetId="18" r:id="rId18"/>
+    <sheet name="lr_0.0019" sheetId="19" r:id="rId19"/>
+    <sheet name="lr_0.002" sheetId="20" r:id="rId20"/>
+    <sheet name="lr_0.0021" sheetId="21" r:id="rId21"/>
+    <sheet name="lr_0.0022" sheetId="22" r:id="rId22"/>
+    <sheet name="lr_0.0023" sheetId="23" r:id="rId23"/>
+    <sheet name="lr_0.0024" sheetId="24" r:id="rId24"/>
+    <sheet name="lr_0.0025" sheetId="25" r:id="rId25"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="1">
   <si>
     <t>window_size</t>
   </si>
@@ -37,8 +46,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -52,15 +61,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="238"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -99,34 +99,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normalny" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Pakiet Office 2007–2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -164,7 +155,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Pakiet Office 2007–2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -198,7 +189,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -233,10 +223,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Pakiet Office 2007–2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -409,11 +398,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -433,7 +422,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2" s="1">
         <v>4</v>
       </c>
@@ -441,64 +430,64 @@
         <v>1.166371324708068</v>
       </c>
       <c r="C2">
-        <v>1.8680393980222909</v>
+        <v>1.868039398022291</v>
       </c>
       <c r="D2">
-        <v>2.6863298646974481</v>
+        <v>2.686329864697448</v>
       </c>
       <c r="E2">
         <v>3.881849615029723</v>
       </c>
       <c r="F2">
-        <v>4.7639766212547627</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>4.763976621254763</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1">
         <v>8</v>
       </c>
       <c r="B3">
-        <v>2.3721077380541562</v>
+        <v>2.372107738054156</v>
       </c>
       <c r="C3">
-        <v>3.3535940166677598</v>
+        <v>3.35359401666776</v>
       </c>
       <c r="D3">
-        <v>5.3631954302421088</v>
+        <v>5.363195430242109</v>
       </c>
       <c r="E3">
-        <v>7.3752288031421926</v>
+        <v>7.375228803142193</v>
       </c>
       <c r="F3">
-        <v>9.2555178962547853</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>9.255517896254785</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1">
         <v>12</v>
       </c>
       <c r="B4">
-        <v>3.0820102107017018</v>
+        <v>3.082010210701702</v>
       </c>
       <c r="C4">
-        <v>5.2770069039586103</v>
+        <v>5.27700690395861</v>
       </c>
       <c r="D4">
-        <v>8.3593223834437165</v>
+        <v>8.359322383443716</v>
       </c>
       <c r="E4">
-        <v>11.333090211512751</v>
+        <v>11.33309021151275</v>
       </c>
       <c r="F4">
-        <v>14.267303569888529</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>14.26730356988853</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1">
         <v>16</v>
       </c>
       <c r="B5">
-        <v>4.7786380609247567</v>
+        <v>4.778638060924757</v>
       </c>
       <c r="C5">
         <v>7.078164937690075</v>
@@ -510,30 +499,30 @@
         <v>14.8760224222611</v>
       </c>
       <c r="F5">
-        <v>18.609062517101879</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>18.60906251710188</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="1">
         <v>20</v>
       </c>
       <c r="B6">
-        <v>4.7611247242292967</v>
+        <v>4.761124724229297</v>
       </c>
       <c r="C6">
-        <v>8.7702696231974411</v>
+        <v>8.770269623197441</v>
       </c>
       <c r="D6">
         <v>13.55562326051486</v>
       </c>
       <c r="E6">
-        <v>18.325738029708059</v>
+        <v>18.32573802970806</v>
       </c>
       <c r="F6">
-        <v>21.760127522876889</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>21.76012752287689</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="1">
         <v>24</v>
       </c>
@@ -541,44 +530,44 @@
         <v>6.694220704766475</v>
       </c>
       <c r="C7">
-        <v>9.8876710949085336</v>
+        <v>9.887671094908534</v>
       </c>
       <c r="D7">
         <v>15.84108629838317</v>
       </c>
       <c r="E7">
-        <v>21.901100817585981</v>
+        <v>21.90110081758598</v>
       </c>
       <c r="F7">
         <v>27.09485847080677</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8" s="1">
         <v>28</v>
       </c>
       <c r="B8">
-        <v>6.4142133695838659</v>
+        <v>6.414213369583866</v>
       </c>
       <c r="C8">
-        <v>12.122713820506361</v>
+        <v>12.12271382050636</v>
       </c>
       <c r="D8">
-        <v>18.524489598068971</v>
+        <v>18.52448959806897</v>
       </c>
       <c r="E8">
         <v>25.11465740706371</v>
       </c>
       <c r="F8">
-        <v>30.822759088591411</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>30.82275908859141</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="1">
         <v>32</v>
       </c>
       <c r="B9">
-        <v>8.3305561009290496</v>
+        <v>8.33055610092905</v>
       </c>
       <c r="C9">
         <v>13.5284046585742</v>
@@ -590,27 +579,38 @@
         <v>28.1159014652123</v>
       </c>
       <c r="F9">
-        <v>35.274467843265377</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>35.27446784326538</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="1">
         <v>36</v>
       </c>
       <c r="B10">
-        <v>7.9604462674065806</v>
+        <v>7.960446267406581</v>
       </c>
       <c r="C10">
         <v>15.26757455388748</v>
       </c>
       <c r="D10">
-        <v>23.330114076888581</v>
+        <v>23.33011407688858</v>
       </c>
       <c r="E10">
-        <v>31.413868575804511</v>
-      </c>
-      <c r="F10" s="3">
-        <v>39.303382681108211</v>
+        <v>31.41386857580451</v>
+      </c>
+      <c r="F10">
+        <v>39.30338268110821</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1">
+        <v>40</v>
+      </c>
+      <c r="E11">
+        <v>34.11922795584183</v>
+      </c>
+      <c r="F11" s="2">
+        <v>42.94276963460192</v>
       </c>
     </row>
   </sheetData>
@@ -619,11 +619,11 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -643,27 +643,27 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2" s="1">
         <v>4</v>
       </c>
       <c r="B2">
-        <v>1.3530658799660329</v>
+        <v>1.353065879966033</v>
       </c>
       <c r="C2">
-        <v>2.1454914813280328</v>
+        <v>2.145491481328033</v>
       </c>
       <c r="D2">
-        <v>3.0818288987367328</v>
+        <v>3.081828898736733</v>
       </c>
       <c r="E2">
-        <v>4.1754813112027458</v>
+        <v>4.175481311202746</v>
       </c>
       <c r="F2">
-        <v>4.2409817690074334</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>4.240981769007433</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1">
         <v>8</v>
       </c>
@@ -671,30 +671,30 @@
         <v>2.289263361050943</v>
       </c>
       <c r="C3">
-        <v>4.0617340289818751</v>
+        <v>4.061734028981875</v>
       </c>
       <c r="D3">
-        <v>5.9002827803290891</v>
+        <v>5.900282780329089</v>
       </c>
       <c r="E3">
-        <v>7.6926170005360071</v>
+        <v>7.692617000536007</v>
       </c>
       <c r="F3">
-        <v>5.6131572127963532</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>5.613157212796353</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1">
         <v>12</v>
       </c>
       <c r="B4">
-        <v>3.4347022224946908</v>
+        <v>3.434702222494691</v>
       </c>
       <c r="C4">
-        <v>5.9547322444649913</v>
+        <v>5.954732244464991</v>
       </c>
       <c r="D4">
-        <v>8.8560330257250754</v>
+        <v>8.856033025725075</v>
       </c>
       <c r="E4">
         <v>11.74150646608704</v>
@@ -703,15 +703,15 @@
         <v>12.93967157040116</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5" s="1">
         <v>16</v>
       </c>
       <c r="B5">
-        <v>4.0565773300105317</v>
+        <v>4.056577330010532</v>
       </c>
       <c r="C5">
-        <v>7.8547469370690663</v>
+        <v>7.854746937069066</v>
       </c>
       <c r="D5">
         <v>11.56506197484067</v>
@@ -723,12 +723,12 @@
         <v>13.10334191040665</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6" s="1">
         <v>20</v>
       </c>
       <c r="B6">
-        <v>5.2486552864437437</v>
+        <v>5.248655286443744</v>
       </c>
       <c r="C6">
         <v>9.498323238544593</v>
@@ -737,18 +737,18 @@
         <v>14.1007029956794</v>
       </c>
       <c r="E6">
-        <v>18.665033652594239</v>
+        <v>18.66503365259424</v>
       </c>
       <c r="F6">
         <v>21.11099106261554</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7" s="1">
         <v>24</v>
       </c>
       <c r="B7">
-        <v>5.7532903882706998</v>
+        <v>5.7532903882707</v>
       </c>
       <c r="C7">
         <v>11.18831676790168</v>
@@ -757,38 +757,38 @@
         <v>16.64210851102683</v>
       </c>
       <c r="E7">
-        <v>21.978363926397069</v>
+        <v>21.97836392639707</v>
       </c>
       <c r="F7">
-        <v>27.148345328519088</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>27.14834532851909</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="1">
         <v>28</v>
       </c>
       <c r="B8">
-        <v>6.9534575595371733</v>
+        <v>6.953457559537173</v>
       </c>
       <c r="C8">
         <v>12.87336765520485</v>
       </c>
       <c r="D8">
-        <v>19.056530691652931</v>
+        <v>19.05653069165293</v>
       </c>
       <c r="E8">
-        <v>25.092104515755921</v>
+        <v>25.09210451575592</v>
       </c>
       <c r="F8">
-        <v>29.603932954245579</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>29.60393295424558</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="1">
         <v>32</v>
       </c>
       <c r="B9">
-        <v>7.4208380575720652</v>
+        <v>7.420838057572065</v>
       </c>
       <c r="C9">
         <v>14.33203903994921</v>
@@ -797,30 +797,1934 @@
         <v>21.86019220811465</v>
       </c>
       <c r="E9">
-        <v>28.513910555062669</v>
+        <v>28.51391055506267</v>
       </c>
       <c r="F9">
-        <v>15.491621469010649</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>15.49162146901065</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="1">
         <v>36</v>
       </c>
       <c r="B10">
-        <v>8.5109598548896006</v>
+        <v>8.510959854889601</v>
       </c>
       <c r="C10">
-        <v>16.046370438151719</v>
+        <v>16.04637043815172</v>
       </c>
       <c r="D10">
         <v>23.86133445626108</v>
       </c>
       <c r="E10">
-        <v>32.021569365745343</v>
+        <v>32.02156936574534</v>
       </c>
       <c r="F10" s="2">
-        <v>39.157568823439497</v>
+        <v>39.1575688234395</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1">
+        <v>40</v>
+      </c>
+      <c r="D11">
+        <v>25.88718480002017</v>
+      </c>
+      <c r="E11">
+        <v>34.64641014321645</v>
+      </c>
+      <c r="F11">
+        <v>20.40572681230591</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>1.180735892240975</v>
+      </c>
+      <c r="C2">
+        <v>1.5139114323068</v>
+      </c>
+      <c r="D2">
+        <v>2.991297540498927</v>
+      </c>
+      <c r="E2">
+        <v>3.54834038573146</v>
+      </c>
+      <c r="F2">
+        <v>4.879330919835413</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>2.532105390592356</v>
+      </c>
+      <c r="C3">
+        <v>3.186368672714365</v>
+      </c>
+      <c r="D3">
+        <v>5.400946643753747</v>
+      </c>
+      <c r="E3">
+        <v>7.322833450649611</v>
+      </c>
+      <c r="F3">
+        <v>9.024480524955477</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>3.057728502581739</v>
+      </c>
+      <c r="C4">
+        <v>4.648749293617827</v>
+      </c>
+      <c r="D4">
+        <v>8.290071912418258</v>
+      </c>
+      <c r="E4">
+        <v>11.15117393891288</v>
+      </c>
+      <c r="F4">
+        <v>14.06654344274632</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>3.853519409562633</v>
+      </c>
+      <c r="C5">
+        <v>6.613419836291932</v>
+      </c>
+      <c r="D5">
+        <v>10.81474532933443</v>
+      </c>
+      <c r="E5">
+        <v>14.5888689706592</v>
+      </c>
+      <c r="F5" s="2">
+        <v>18.19367060152878</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1">
+        <v>20</v>
+      </c>
+      <c r="B6">
+        <v>0.01058668904812243</v>
+      </c>
+      <c r="C6">
+        <v>0.01270677464964232</v>
+      </c>
+      <c r="D6">
+        <v>0.0163051813195206</v>
+      </c>
+      <c r="E6">
+        <v>0.02015976906073627</v>
+      </c>
+      <c r="F6">
+        <v>0.02321370583104964</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1">
+        <v>24</v>
+      </c>
+      <c r="B7">
+        <v>0.01062784708080187</v>
+      </c>
+      <c r="C7">
+        <v>0.0136212972503807</v>
+      </c>
+      <c r="D7">
+        <v>0.01674062588148688</v>
+      </c>
+      <c r="E7">
+        <v>0.02004915440608693</v>
+      </c>
+      <c r="F7">
+        <v>0.02291740447403532</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1">
+        <v>28</v>
+      </c>
+      <c r="B8">
+        <v>0.01079600391210123</v>
+      </c>
+      <c r="C8">
+        <v>0.01324363152894825</v>
+      </c>
+      <c r="D8">
+        <v>0.01631134489400786</v>
+      </c>
+      <c r="E8">
+        <v>0.01926269708955146</v>
+      </c>
+      <c r="F8">
+        <v>0.02234941492809503</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>0.01147397409223248</v>
+      </c>
+      <c r="C9">
+        <v>0.01469488234747712</v>
+      </c>
+      <c r="D9">
+        <v>0.01821850980091949</v>
+      </c>
+      <c r="E9">
+        <v>0.02070690031852247</v>
+      </c>
+      <c r="F9">
+        <v>0.02501829409364546</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1">
+        <v>36</v>
+      </c>
+      <c r="B10">
+        <v>0.01022186242279398</v>
+      </c>
+      <c r="C10">
+        <v>0.01271081387600837</v>
+      </c>
+      <c r="D10">
+        <v>0.01555001867933579</v>
+      </c>
+      <c r="E10">
+        <v>0.01848396944257059</v>
+      </c>
+      <c r="F10">
+        <v>0.02139717161103874</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>1.165913239967088</v>
+      </c>
+      <c r="C2">
+        <v>1.916088903201703</v>
+      </c>
+      <c r="D2">
+        <v>2.99586879963905</v>
+      </c>
+      <c r="E2">
+        <v>3.881306942001055</v>
+      </c>
+      <c r="F2">
+        <v>4.859374979348208</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>2.128383620730375</v>
+      </c>
+      <c r="C3">
+        <v>3.50325632921447</v>
+      </c>
+      <c r="D3">
+        <v>5.489327150569115</v>
+      </c>
+      <c r="E3">
+        <v>7.463442768228074</v>
+      </c>
+      <c r="F3">
+        <v>9.15993958739805</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>3.056307119669847</v>
+      </c>
+      <c r="C4">
+        <v>5.617262213377903</v>
+      </c>
+      <c r="D4">
+        <v>8.241263999491517</v>
+      </c>
+      <c r="E4">
+        <v>11.36273089036308</v>
+      </c>
+      <c r="F4">
+        <v>14.18855149921344</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>3.851894890565818</v>
+      </c>
+      <c r="C5">
+        <v>7.163160970960718</v>
+      </c>
+      <c r="D5">
+        <v>10.98724234944478</v>
+      </c>
+      <c r="E5">
+        <v>14.75923204686198</v>
+      </c>
+      <c r="F5" s="2">
+        <v>18.50198723770694</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1">
+        <v>20</v>
+      </c>
+      <c r="B6">
+        <v>0.009530654909670543</v>
+      </c>
+      <c r="C6">
+        <v>0.0127586835418554</v>
+      </c>
+      <c r="D6">
+        <v>0.01624337614632821</v>
+      </c>
+      <c r="E6">
+        <v>0.02002202163582283</v>
+      </c>
+      <c r="F6">
+        <v>0.02335666349144591</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1">
+        <v>24</v>
+      </c>
+      <c r="B7">
+        <v>0.01025013836766687</v>
+      </c>
+      <c r="C7">
+        <v>0.01362102262295991</v>
+      </c>
+      <c r="D7">
+        <v>0.01678138001967269</v>
+      </c>
+      <c r="E7">
+        <v>0.01978564028784009</v>
+      </c>
+      <c r="F7">
+        <v>0.02315451205416307</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1">
+        <v>28</v>
+      </c>
+      <c r="B8">
+        <v>0.01029113954463415</v>
+      </c>
+      <c r="C8">
+        <v>0.01323763004679261</v>
+      </c>
+      <c r="D8">
+        <v>0.01623657292402409</v>
+      </c>
+      <c r="E8">
+        <v>0.01921387221590658</v>
+      </c>
+      <c r="F8">
+        <v>0.02259349203355251</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>0.01087435313309281</v>
+      </c>
+      <c r="C9">
+        <v>0.01475301085162568</v>
+      </c>
+      <c r="D9">
+        <v>0.0181127890003766</v>
+      </c>
+      <c r="E9">
+        <v>0.02052626479828</v>
+      </c>
+      <c r="F9">
+        <v>0.02473230268601689</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1">
+        <v>36</v>
+      </c>
+      <c r="B10">
+        <v>0.009824655533192587</v>
+      </c>
+      <c r="C10">
+        <v>0.01276253724925273</v>
+      </c>
+      <c r="D10">
+        <v>0.01554700471526318</v>
+      </c>
+      <c r="E10">
+        <v>0.01848290158030226</v>
+      </c>
+      <c r="F10">
+        <v>0.02138941194108888</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>1.172638915973462</v>
+      </c>
+      <c r="C2">
+        <v>2.118020401360946</v>
+      </c>
+      <c r="D2">
+        <v>2.860400883713359</v>
+      </c>
+      <c r="E2">
+        <v>4.032234674881079</v>
+      </c>
+      <c r="F2">
+        <v>4.909056120413992</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>2.077984901471337</v>
+      </c>
+      <c r="C3">
+        <v>3.604984216732458</v>
+      </c>
+      <c r="D3">
+        <v>5.544939171127397</v>
+      </c>
+      <c r="E3">
+        <v>7.478979031747426</v>
+      </c>
+      <c r="F3">
+        <v>9.23440955906692</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>3.055166274537154</v>
+      </c>
+      <c r="C4">
+        <v>5.756600829322722</v>
+      </c>
+      <c r="D4">
+        <v>8.416070626161334</v>
+      </c>
+      <c r="E4">
+        <v>11.40996761124202</v>
+      </c>
+      <c r="F4">
+        <v>14.31034176719726</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>3.849452349665607</v>
+      </c>
+      <c r="C5">
+        <v>7.452231097599806</v>
+      </c>
+      <c r="D5">
+        <v>11.07296636742675</v>
+      </c>
+      <c r="E5">
+        <v>14.84412524295221</v>
+      </c>
+      <c r="F5" s="2">
+        <v>18.58731090472421</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1">
+        <v>20</v>
+      </c>
+      <c r="B6">
+        <v>0.0091901894916413</v>
+      </c>
+      <c r="C6">
+        <v>0.0127338115914046</v>
+      </c>
+      <c r="D6">
+        <v>0.01627263516573124</v>
+      </c>
+      <c r="E6">
+        <v>0.02023513059408874</v>
+      </c>
+      <c r="F6">
+        <v>0.02334921155955999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1">
+        <v>24</v>
+      </c>
+      <c r="B7">
+        <v>0.01023912453688923</v>
+      </c>
+      <c r="C7">
+        <v>0.0136946232429537</v>
+      </c>
+      <c r="D7">
+        <v>0.01667665091957803</v>
+      </c>
+      <c r="E7">
+        <v>0.02008241810832808</v>
+      </c>
+      <c r="F7">
+        <v>0.0231313223540825</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1">
+        <v>28</v>
+      </c>
+      <c r="B8">
+        <v>0.01009350828823338</v>
+      </c>
+      <c r="C8">
+        <v>0.01325333960512638</v>
+      </c>
+      <c r="D8">
+        <v>0.01630106644516227</v>
+      </c>
+      <c r="E8">
+        <v>0.01981201946928543</v>
+      </c>
+      <c r="F8">
+        <v>0.02258666508368636</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>0.0109350936279821</v>
+      </c>
+      <c r="C9">
+        <v>0.01484601307941369</v>
+      </c>
+      <c r="D9">
+        <v>0.01818406130222435</v>
+      </c>
+      <c r="E9">
+        <v>0.0206321193186582</v>
+      </c>
+      <c r="F9">
+        <v>0.02381102638552089</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1">
+        <v>36</v>
+      </c>
+      <c r="B10">
+        <v>0.009875651811774288</v>
+      </c>
+      <c r="C10">
+        <v>0.01257048589295452</v>
+      </c>
+      <c r="D10">
+        <v>0.01554705588081669</v>
+      </c>
+      <c r="E10">
+        <v>0.01849952736293433</v>
+      </c>
+      <c r="F10">
+        <v>0.02139032546401413</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>1.181916638719745</v>
+      </c>
+      <c r="C2">
+        <v>2.122288325220799</v>
+      </c>
+      <c r="D2">
+        <v>2.854778715857765</v>
+      </c>
+      <c r="E2">
+        <v>4.032131004849307</v>
+      </c>
+      <c r="F2">
+        <v>4.909512255313182</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>1.913933067274996</v>
+      </c>
+      <c r="C3">
+        <v>3.703475080101889</v>
+      </c>
+      <c r="D3">
+        <v>5.642111273536099</v>
+      </c>
+      <c r="E3">
+        <v>7.556789843432223</v>
+      </c>
+      <c r="F3">
+        <v>9.321712500976616</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>3.054792430634817</v>
+      </c>
+      <c r="C4">
+        <v>5.766123807742043</v>
+      </c>
+      <c r="D4">
+        <v>8.511769912920402</v>
+      </c>
+      <c r="E4">
+        <v>11.34258348723347</v>
+      </c>
+      <c r="F4">
+        <v>14.36525722306585</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>3.855213076878981</v>
+      </c>
+      <c r="C5">
+        <v>7.453394122089172</v>
+      </c>
+      <c r="D5">
+        <v>11.10473317320279</v>
+      </c>
+      <c r="E5">
+        <v>14.89711527574312</v>
+      </c>
+      <c r="F5" s="2">
+        <v>18.66262628683114</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1">
+        <v>20</v>
+      </c>
+      <c r="B6">
+        <v>0.009193452610084323</v>
+      </c>
+      <c r="C6">
+        <v>0.01287577892250763</v>
+      </c>
+      <c r="D6">
+        <v>0.0163058436346179</v>
+      </c>
+      <c r="E6">
+        <v>0.02031006224980779</v>
+      </c>
+      <c r="F6">
+        <v>0.02316599558517233</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1">
+        <v>24</v>
+      </c>
+      <c r="B7">
+        <v>0.0102580592190788</v>
+      </c>
+      <c r="C7">
+        <v>0.01366346230479046</v>
+      </c>
+      <c r="D7">
+        <v>0.01669771849634294</v>
+      </c>
+      <c r="E7">
+        <v>0.02003001055185636</v>
+      </c>
+      <c r="F7">
+        <v>0.02306748239016763</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1">
+        <v>28</v>
+      </c>
+      <c r="B8">
+        <v>0.0101591610658858</v>
+      </c>
+      <c r="C8">
+        <v>0.0133853789078526</v>
+      </c>
+      <c r="D8">
+        <v>0.01627644070672171</v>
+      </c>
+      <c r="E8">
+        <v>0.01945636832025402</v>
+      </c>
+      <c r="F8">
+        <v>0.02256805425610037</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>0.01087185335192323</v>
+      </c>
+      <c r="C9">
+        <v>0.01426949975574008</v>
+      </c>
+      <c r="D9">
+        <v>0.01766411285969649</v>
+      </c>
+      <c r="E9">
+        <v>0.02046037649886827</v>
+      </c>
+      <c r="F9">
+        <v>0.02399814482342062</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1">
+        <v>36</v>
+      </c>
+      <c r="B10">
+        <v>0.009824391054728557</v>
+      </c>
+      <c r="C10">
+        <v>0.01258433790292419</v>
+      </c>
+      <c r="D10">
+        <v>0.01555689416916976</v>
+      </c>
+      <c r="E10">
+        <v>0.01855539729203382</v>
+      </c>
+      <c r="F10">
+        <v>0.02138128248633468</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>1.165810183496814</v>
+      </c>
+      <c r="C2">
+        <v>2.080637478991505</v>
+      </c>
+      <c r="D2">
+        <v>3.091309575628456</v>
+      </c>
+      <c r="E2">
+        <v>3.872242929003171</v>
+      </c>
+      <c r="F2">
+        <v>5.027485921273889</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>1.902842259192199</v>
+      </c>
+      <c r="C3">
+        <v>3.710124779796226</v>
+      </c>
+      <c r="D3">
+        <v>5.609922185404439</v>
+      </c>
+      <c r="E3">
+        <v>7.52307316713997</v>
+      </c>
+      <c r="F3">
+        <v>9.4565438866083</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>3.052097979229302</v>
+      </c>
+      <c r="C4">
+        <v>5.503956479473447</v>
+      </c>
+      <c r="D4">
+        <v>8.580918342501059</v>
+      </c>
+      <c r="E4">
+        <v>11.09640475636421</v>
+      </c>
+      <c r="F4">
+        <v>14.21903622481619</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>3.827608062544587</v>
+      </c>
+      <c r="C5">
+        <v>7.340168057458588</v>
+      </c>
+      <c r="D5">
+        <v>11.15996944838743</v>
+      </c>
+      <c r="E5">
+        <v>14.87860295860934</v>
+      </c>
+      <c r="F5" s="2">
+        <v>18.64183794086722</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1">
+        <v>20</v>
+      </c>
+      <c r="B6">
+        <v>0.009220321345022651</v>
+      </c>
+      <c r="C6">
+        <v>0.01281481502229034</v>
+      </c>
+      <c r="D6">
+        <v>0.01630971930620029</v>
+      </c>
+      <c r="E6">
+        <v>0.02009119097882563</v>
+      </c>
+      <c r="F6">
+        <v>0.02332494348050179</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1">
+        <v>24</v>
+      </c>
+      <c r="B7">
+        <v>0.01014808412150538</v>
+      </c>
+      <c r="C7">
+        <v>0.01371059006391708</v>
+      </c>
+      <c r="D7">
+        <v>0.01667198168067855</v>
+      </c>
+      <c r="E7">
+        <v>0.01996342835740499</v>
+      </c>
+      <c r="F7">
+        <v>0.02302341034764799</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1">
+        <v>28</v>
+      </c>
+      <c r="B8">
+        <v>0.01007833256928874</v>
+      </c>
+      <c r="C8">
+        <v>0.01339848394206114</v>
+      </c>
+      <c r="D8">
+        <v>0.01635165606806304</v>
+      </c>
+      <c r="E8">
+        <v>0.01932069671687185</v>
+      </c>
+      <c r="F8">
+        <v>0.02246024895428765</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>0.01090025655718766</v>
+      </c>
+      <c r="C9">
+        <v>0.0142229623112132</v>
+      </c>
+      <c r="D9">
+        <v>0.01726020807544938</v>
+      </c>
+      <c r="E9">
+        <v>0.02047976401688644</v>
+      </c>
+      <c r="F9">
+        <v>0.02410637651918152</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1">
+        <v>36</v>
+      </c>
+      <c r="B10">
+        <v>0.009897943375340015</v>
+      </c>
+      <c r="C10">
+        <v>0.01264479599407782</v>
+      </c>
+      <c r="D10">
+        <v>0.01557313418037465</v>
+      </c>
+      <c r="E10">
+        <v>0.01840474335600957</v>
+      </c>
+      <c r="F10">
+        <v>0.02139150211995373</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>1.172652035480896</v>
+      </c>
+      <c r="C2">
+        <v>1.833072199121024</v>
+      </c>
+      <c r="D2">
+        <v>3.098646064615701</v>
+      </c>
+      <c r="E2">
+        <v>3.873533983151768</v>
+      </c>
+      <c r="F2">
+        <v>4.979835888535069</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>1.883976273743102</v>
+      </c>
+      <c r="C3">
+        <v>3.730379081187849</v>
+      </c>
+      <c r="D3">
+        <v>5.609763479039309</v>
+      </c>
+      <c r="E3">
+        <v>7.521663750372728</v>
+      </c>
+      <c r="F3">
+        <v>9.395993869276994</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>3.048306387152861</v>
+      </c>
+      <c r="C4">
+        <v>5.587725528457533</v>
+      </c>
+      <c r="D4">
+        <v>8.564268527819552</v>
+      </c>
+      <c r="E4">
+        <v>11.13798473243001</v>
+      </c>
+      <c r="F4">
+        <v>14.24414150787349</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>3.842502199908704</v>
+      </c>
+      <c r="C5">
+        <v>7.254313513191043</v>
+      </c>
+      <c r="D5">
+        <v>11.18556524476118</v>
+      </c>
+      <c r="E5">
+        <v>14.90006429092049</v>
+      </c>
+      <c r="F5" s="2">
+        <v>18.59787046353604</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1">
+        <v>20</v>
+      </c>
+      <c r="B6">
+        <v>0.009255071950839355</v>
+      </c>
+      <c r="C6">
+        <v>0.01281824313158406</v>
+      </c>
+      <c r="D6">
+        <v>0.01611051280145393</v>
+      </c>
+      <c r="E6">
+        <v>0.02010735954880846</v>
+      </c>
+      <c r="F6">
+        <v>0.02324954198956744</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1">
+        <v>24</v>
+      </c>
+      <c r="B7">
+        <v>0.01007090934780634</v>
+      </c>
+      <c r="C7">
+        <v>0.01376667856528585</v>
+      </c>
+      <c r="D7">
+        <v>0.01668266310866832</v>
+      </c>
+      <c r="E7">
+        <v>0.01997254074021241</v>
+      </c>
+      <c r="F7">
+        <v>0.02300618749811124</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1">
+        <v>28</v>
+      </c>
+      <c r="B8">
+        <v>0.009932523938319783</v>
+      </c>
+      <c r="C8">
+        <v>0.01347613632812455</v>
+      </c>
+      <c r="D8">
+        <v>0.01631215995323702</v>
+      </c>
+      <c r="E8">
+        <v>0.01933621432929549</v>
+      </c>
+      <c r="F8">
+        <v>0.02223841845667911</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>0.01089114781399653</v>
+      </c>
+      <c r="C9">
+        <v>0.01409964987033936</v>
+      </c>
+      <c r="D9">
+        <v>0.01743029814419651</v>
+      </c>
+      <c r="E9">
+        <v>0.02065270784668275</v>
+      </c>
+      <c r="F9">
+        <v>0.02487733653198948</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1">
+        <v>36</v>
+      </c>
+      <c r="B10">
+        <v>0.009827936515239248</v>
+      </c>
+      <c r="C10">
+        <v>0.01259611087396811</v>
+      </c>
+      <c r="D10">
+        <v>0.01555538380769059</v>
+      </c>
+      <c r="E10">
+        <v>0.01843367585743779</v>
+      </c>
+      <c r="F10">
+        <v>0.02139778368958794</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>1.169498044618898</v>
+      </c>
+      <c r="C2">
+        <v>2.115517735066863</v>
+      </c>
+      <c r="D2">
+        <v>2.985131473124207</v>
+      </c>
+      <c r="E2">
+        <v>4.018018434624234</v>
+      </c>
+      <c r="F2">
+        <v>4.901000809222952</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>1.924740027377924</v>
+      </c>
+      <c r="C3">
+        <v>3.745212488480888</v>
+      </c>
+      <c r="D3">
+        <v>5.613115530371513</v>
+      </c>
+      <c r="E3">
+        <v>7.497035265504334</v>
+      </c>
+      <c r="F3">
+        <v>9.416298133891829</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>3.05080903453822</v>
+      </c>
+      <c r="C4">
+        <v>5.770073339644402</v>
+      </c>
+      <c r="D4">
+        <v>8.390838230606155</v>
+      </c>
+      <c r="E4">
+        <v>11.204982632758</v>
+      </c>
+      <c r="F4">
+        <v>14.28447661411472</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>3.839146106701703</v>
+      </c>
+      <c r="C5">
+        <v>7.444749215627393</v>
+      </c>
+      <c r="D5">
+        <v>11.09312655823558</v>
+      </c>
+      <c r="E5">
+        <v>14.52658683287039</v>
+      </c>
+      <c r="F5" s="2">
+        <v>18.36419078340124</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1">
+        <v>20</v>
+      </c>
+      <c r="B6">
+        <v>0.009206707000454608</v>
+      </c>
+      <c r="C6">
+        <v>0.01296224628579224</v>
+      </c>
+      <c r="D6">
+        <v>0.01617023370623803</v>
+      </c>
+      <c r="E6">
+        <v>0.02017292042472078</v>
+      </c>
+      <c r="F6">
+        <v>0.02327260245356363</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1">
+        <v>24</v>
+      </c>
+      <c r="B7">
+        <v>0.01011699327074175</v>
+      </c>
+      <c r="C7">
+        <v>0.01391607270542816</v>
+      </c>
+      <c r="D7">
+        <v>0.01664171302554543</v>
+      </c>
+      <c r="E7">
+        <v>0.02003524008481625</v>
+      </c>
+      <c r="F7">
+        <v>0.0231063446382727</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1">
+        <v>28</v>
+      </c>
+      <c r="B8">
+        <v>0.01016620177634242</v>
+      </c>
+      <c r="C8">
+        <v>0.01328585760111425</v>
+      </c>
+      <c r="D8">
+        <v>0.01631256460921909</v>
+      </c>
+      <c r="E8">
+        <v>0.01925673835962514</v>
+      </c>
+      <c r="F8">
+        <v>0.02272841647406867</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>0.01095016179131141</v>
+      </c>
+      <c r="C9">
+        <v>0.01402220023932398</v>
+      </c>
+      <c r="D9">
+        <v>0.01741662597488993</v>
+      </c>
+      <c r="E9">
+        <v>0.02049665692093166</v>
+      </c>
+      <c r="F9">
+        <v>0.02463659567542418</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1">
+        <v>36</v>
+      </c>
+      <c r="B10">
+        <v>0.009850462534659663</v>
+      </c>
+      <c r="C10">
+        <v>0.01263513018599204</v>
+      </c>
+      <c r="D10">
+        <v>0.01559034349839129</v>
+      </c>
+      <c r="E10">
+        <v>0.01840755371966364</v>
+      </c>
+      <c r="F10">
+        <v>0.02138741092233387</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>1.168281200409765</v>
+      </c>
+      <c r="C2">
+        <v>2.125253109553093</v>
+      </c>
+      <c r="D2">
+        <v>2.830553254077509</v>
+      </c>
+      <c r="E2">
+        <v>4.031049056704894</v>
+      </c>
+      <c r="F2">
+        <v>4.847128992903512</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>1.852769511165533</v>
+      </c>
+      <c r="C3">
+        <v>3.734057021442574</v>
+      </c>
+      <c r="D3">
+        <v>5.666710144216569</v>
+      </c>
+      <c r="E3">
+        <v>7.55488306873464</v>
+      </c>
+      <c r="F3">
+        <v>9.268624967098694</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>3.0400785721741</v>
+      </c>
+      <c r="C4">
+        <v>5.770207182138026</v>
+      </c>
+      <c r="D4">
+        <v>8.421551934748402</v>
+      </c>
+      <c r="E4">
+        <v>11.16446176993202</v>
+      </c>
+      <c r="F4">
+        <v>14.37438998136398</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>3.837101093826962</v>
+      </c>
+      <c r="C5">
+        <v>7.457597781868387</v>
+      </c>
+      <c r="D5">
+        <v>11.13573559405408</v>
+      </c>
+      <c r="E5">
+        <v>14.30829174781956</v>
+      </c>
+      <c r="F5" s="2">
+        <v>18.42905162186413</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1">
+        <v>20</v>
+      </c>
+      <c r="B6">
+        <v>0.009347542767461652</v>
+      </c>
+      <c r="C6">
+        <v>0.01284243552084798</v>
+      </c>
+      <c r="D6">
+        <v>0.0162548828499803</v>
+      </c>
+      <c r="E6">
+        <v>0.02013390009010813</v>
+      </c>
+      <c r="F6">
+        <v>0.02321995687987996</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1">
+        <v>24</v>
+      </c>
+      <c r="B7">
+        <v>0.01010742519616106</v>
+      </c>
+      <c r="C7">
+        <v>0.01358683219515904</v>
+      </c>
+      <c r="D7">
+        <v>0.01665666863404317</v>
+      </c>
+      <c r="E7">
+        <v>0.01989952779205461</v>
+      </c>
+      <c r="F7">
+        <v>0.02292329847682643</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1">
+        <v>28</v>
+      </c>
+      <c r="B8">
+        <v>0.01009958740362093</v>
+      </c>
+      <c r="C8">
+        <v>0.01341313681693257</v>
+      </c>
+      <c r="D8">
+        <v>0.01622792785091775</v>
+      </c>
+      <c r="E8">
+        <v>0.01927643453155104</v>
+      </c>
+      <c r="F8">
+        <v>0.02239172941646212</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>0.010896705986205</v>
+      </c>
+      <c r="C9">
+        <v>0.0140950588994875</v>
+      </c>
+      <c r="D9">
+        <v>0.01740332954635373</v>
+      </c>
+      <c r="E9">
+        <v>0.02013265882910258</v>
+      </c>
+      <c r="F9">
+        <v>0.02448514902301458</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1">
+        <v>36</v>
+      </c>
+      <c r="B10">
+        <v>0.009812179582635675</v>
+      </c>
+      <c r="C10">
+        <v>0.01262852693338816</v>
+      </c>
+      <c r="D10">
+        <v>0.01552973430459892</v>
+      </c>
+      <c r="E10">
+        <v>0.0184094263064898</v>
+      </c>
+      <c r="F10">
+        <v>0.02135080969542084</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>1.157710203972401</v>
+      </c>
+      <c r="C2">
+        <v>2.099484340868362</v>
+      </c>
+      <c r="D2">
+        <v>3.020492239983016</v>
+      </c>
+      <c r="E2">
+        <v>3.898275830005318</v>
+      </c>
+      <c r="F2">
+        <v>4.977003831673063</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>1.885773714386414</v>
+      </c>
+      <c r="C3">
+        <v>3.690814685882129</v>
+      </c>
+      <c r="D3">
+        <v>5.616251963065857</v>
+      </c>
+      <c r="E3">
+        <v>7.485414016930927</v>
+      </c>
+      <c r="F3">
+        <v>9.21585247509671</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>3.035271922109347</v>
+      </c>
+      <c r="C4">
+        <v>5.553398363468179</v>
+      </c>
+      <c r="D4">
+        <v>8.480006619015969</v>
+      </c>
+      <c r="E4">
+        <v>11.38136431448083</v>
+      </c>
+      <c r="F4">
+        <v>14.11546164231329</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>3.743510704860933</v>
+      </c>
+      <c r="C5">
+        <v>7.375718279378966</v>
+      </c>
+      <c r="D5">
+        <v>11.17991720603506</v>
+      </c>
+      <c r="E5">
+        <v>14.28543638894801</v>
+      </c>
+      <c r="F5" s="2">
+        <v>18.28759583684302</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1">
+        <v>20</v>
+      </c>
+      <c r="B6">
+        <v>0.009290891795146285</v>
+      </c>
+      <c r="C6">
+        <v>0.0128938359689267</v>
+      </c>
+      <c r="D6">
+        <v>0.01577667673369904</v>
+      </c>
+      <c r="E6">
+        <v>0.02017509309987606</v>
+      </c>
+      <c r="F6">
+        <v>0.02341345671741435</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1">
+        <v>24</v>
+      </c>
+      <c r="B7">
+        <v>0.01023233123058765</v>
+      </c>
+      <c r="C7">
+        <v>0.01367448308993148</v>
+      </c>
+      <c r="D7">
+        <v>0.0166245717111621</v>
+      </c>
+      <c r="E7">
+        <v>0.02003366779770817</v>
+      </c>
+      <c r="F7">
+        <v>0.0231634566028115</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1">
+        <v>28</v>
+      </c>
+      <c r="B8">
+        <v>0.01021990904982094</v>
+      </c>
+      <c r="C8">
+        <v>0.01344899259693154</v>
+      </c>
+      <c r="D8">
+        <v>0.01631225332373189</v>
+      </c>
+      <c r="E8">
+        <v>0.01940146974502838</v>
+      </c>
+      <c r="F8">
+        <v>0.02253877172688879</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>0.01064884002033014</v>
+      </c>
+      <c r="C9">
+        <v>0.01410695515503695</v>
+      </c>
+      <c r="D9">
+        <v>0.01737017460611566</v>
+      </c>
+      <c r="E9">
+        <v>0.02061999449049145</v>
+      </c>
+      <c r="F9">
+        <v>0.02384098367001802</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1">
+        <v>36</v>
+      </c>
+      <c r="B10">
+        <v>0.009858417012334522</v>
+      </c>
+      <c r="C10">
+        <v>0.01260784657014215</v>
+      </c>
+      <c r="D10">
+        <v>0.01552141287177208</v>
+      </c>
+      <c r="E10">
+        <v>0.01845677666737591</v>
+      </c>
+      <c r="F10">
+        <v>0.021393391045522</v>
       </c>
     </row>
   </sheetData>
@@ -829,11 +2733,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -853,7 +2757,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2" s="1">
         <v>4</v>
       </c>
@@ -861,39 +2765,39 @@
         <v>1.17236633617516</v>
       </c>
       <c r="C2">
-        <v>1.8663258318503231</v>
+        <v>1.866325831850323</v>
       </c>
       <c r="D2">
         <v>2.856006745563695</v>
       </c>
       <c r="E2">
-        <v>3.9418426776857558</v>
+        <v>3.941842677685756</v>
       </c>
       <c r="F2">
-        <v>4.8374707174373563</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>4.837470717437356</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1">
         <v>8</v>
       </c>
       <c r="B3">
-        <v>2.2240514978789729</v>
+        <v>2.224051497878973</v>
       </c>
       <c r="C3">
-        <v>3.6240263357674949</v>
+        <v>3.624026335767495</v>
       </c>
       <c r="D3">
-        <v>5.5526638394512089</v>
+        <v>5.552663839451209</v>
       </c>
       <c r="E3">
-        <v>7.4518022561092607</v>
+        <v>7.451802256109261</v>
       </c>
       <c r="F3">
-        <v>9.4618322695839225</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>9.461832269583923</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1">
         <v>12</v>
       </c>
@@ -901,59 +2805,59 @@
         <v>3.077783431024415</v>
       </c>
       <c r="C4">
-        <v>5.2769047832621956</v>
+        <v>5.276904783262196</v>
       </c>
       <c r="D4">
-        <v>8.4568155879246216</v>
+        <v>8.456815587924622</v>
       </c>
       <c r="E4">
         <v>11.46119445049683</v>
       </c>
       <c r="F4">
-        <v>14.446159823341819</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>14.44615982334182</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1">
         <v>16</v>
       </c>
       <c r="B5">
-        <v>4.7195571104277363</v>
+        <v>4.719557110427736</v>
       </c>
       <c r="C5">
-        <v>7.2825681054374556</v>
+        <v>7.282568105437456</v>
       </c>
       <c r="D5">
-        <v>11.114605688506421</v>
+        <v>11.11460568850642</v>
       </c>
       <c r="E5">
-        <v>15.045566987858789</v>
+        <v>15.04556698785879</v>
       </c>
       <c r="F5">
         <v>18.85640421102681</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6" s="1">
         <v>20</v>
       </c>
       <c r="B6">
-        <v>4.7496669877834377</v>
+        <v>4.749666987783438</v>
       </c>
       <c r="C6">
-        <v>8.8021390957197436</v>
+        <v>8.802139095719744</v>
       </c>
       <c r="D6">
-        <v>13.681957294039259</v>
+        <v>13.68195729403926</v>
       </c>
       <c r="E6">
         <v>18.47715562119317</v>
       </c>
       <c r="F6">
-        <v>22.109643548665669</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>22.10964354866567</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="1">
         <v>24</v>
       </c>
@@ -964,7 +2868,7 @@
         <v>10.34447710762629</v>
       </c>
       <c r="D7">
-        <v>16.129239732181571</v>
+        <v>16.12923973218157</v>
       </c>
       <c r="E7">
         <v>21.86394520135245</v>
@@ -973,12 +2877,12 @@
         <v>27.13061474852864</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8" s="1">
         <v>28</v>
       </c>
       <c r="B8">
-        <v>6.4186240512059456</v>
+        <v>6.418624051205946</v>
       </c>
       <c r="C8">
         <v>12.13764803738429</v>
@@ -993,44 +2897,1315 @@
         <v>30.93952570235993</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6">
       <c r="A9" s="1">
         <v>32</v>
       </c>
       <c r="B9">
-        <v>8.2253602166499196</v>
+        <v>8.22536021664992</v>
       </c>
       <c r="C9">
-        <v>13.698472880538519</v>
+        <v>13.69847288053852</v>
       </c>
       <c r="D9">
-        <v>20.931203479773799</v>
+        <v>20.9312034797738</v>
       </c>
       <c r="E9">
-        <v>28.209634259039291</v>
+        <v>28.20963425903929</v>
       </c>
       <c r="F9">
-        <v>35.449807106753653</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>35.44980710675365</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="1">
         <v>36</v>
       </c>
       <c r="B10">
-        <v>7.9738371303258972</v>
+        <v>7.973837130325897</v>
       </c>
       <c r="C10">
-        <v>15.318878899793001</v>
+        <v>15.318878899793</v>
       </c>
       <c r="D10">
         <v>23.47162333164864</v>
       </c>
       <c r="E10">
-        <v>31.609872428092402</v>
-      </c>
-      <c r="F10" s="3">
-        <v>39.459051069470263</v>
+        <v>31.6098724280924</v>
+      </c>
+      <c r="F10">
+        <v>39.45905106947026</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1">
+        <v>40</v>
+      </c>
+      <c r="E11">
+        <v>34.35488577960187</v>
+      </c>
+      <c r="F11" s="2">
+        <v>42.68486347285221</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>1.169995439955413</v>
+      </c>
+      <c r="C2">
+        <v>1.79177116037154</v>
+      </c>
+      <c r="D2">
+        <v>3.095795701079608</v>
+      </c>
+      <c r="E2">
+        <v>3.869632224324822</v>
+      </c>
+      <c r="F2">
+        <v>4.955525534102985</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>1.850514230830071</v>
+      </c>
+      <c r="C3">
+        <v>3.710998571540325</v>
+      </c>
+      <c r="D3">
+        <v>5.609261432008508</v>
+      </c>
+      <c r="E3">
+        <v>7.45815502342452</v>
+      </c>
+      <c r="F3">
+        <v>9.145116475500943</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>3.038913017205934</v>
+      </c>
+      <c r="C4">
+        <v>5.556537918220829</v>
+      </c>
+      <c r="D4">
+        <v>8.473708773718633</v>
+      </c>
+      <c r="E4">
+        <v>11.41014113675062</v>
+      </c>
+      <c r="F4">
+        <v>13.91457692568051</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>3.819908115305735</v>
+      </c>
+      <c r="C5">
+        <v>7.292108712057338</v>
+      </c>
+      <c r="D5">
+        <v>11.22157735520183</v>
+      </c>
+      <c r="E5">
+        <v>14.50347374934394</v>
+      </c>
+      <c r="F5" s="2">
+        <v>18.07074930355618</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1">
+        <v>20</v>
+      </c>
+      <c r="B6">
+        <v>0.009397974718105535</v>
+      </c>
+      <c r="C6">
+        <v>0.01258758531500004</v>
+      </c>
+      <c r="D6">
+        <v>0.01603006864806455</v>
+      </c>
+      <c r="E6">
+        <v>0.02014017788643999</v>
+      </c>
+      <c r="F6">
+        <v>0.02326703006855209</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1">
+        <v>24</v>
+      </c>
+      <c r="B7">
+        <v>0.01026488161509147</v>
+      </c>
+      <c r="C7">
+        <v>0.0136692852799923</v>
+      </c>
+      <c r="D7">
+        <v>0.01681314191099794</v>
+      </c>
+      <c r="E7">
+        <v>0.01995832967091052</v>
+      </c>
+      <c r="F7">
+        <v>0.02315387430585003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1">
+        <v>28</v>
+      </c>
+      <c r="B8">
+        <v>0.0102477788837674</v>
+      </c>
+      <c r="C8">
+        <v>0.01356249336827291</v>
+      </c>
+      <c r="D8">
+        <v>0.01658826941738474</v>
+      </c>
+      <c r="E8">
+        <v>0.01932924642763199</v>
+      </c>
+      <c r="F8">
+        <v>0.0226215118301759</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>0.01076538492143184</v>
+      </c>
+      <c r="C9">
+        <v>0.01422073014208186</v>
+      </c>
+      <c r="D9">
+        <v>0.01722177203177774</v>
+      </c>
+      <c r="E9">
+        <v>0.02170934773029487</v>
+      </c>
+      <c r="F9">
+        <v>0.02409294856107406</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1">
+        <v>36</v>
+      </c>
+      <c r="B10">
+        <v>0.00983670393748119</v>
+      </c>
+      <c r="C10">
+        <v>0.01262933355578144</v>
+      </c>
+      <c r="D10">
+        <v>0.01551306541048133</v>
+      </c>
+      <c r="E10">
+        <v>0.01852843624648056</v>
+      </c>
+      <c r="F10">
+        <v>0.02140501427117907</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>1.177469411493634</v>
+      </c>
+      <c r="C2">
+        <v>2.03112918807113</v>
+      </c>
+      <c r="D2">
+        <v>3.01360843903824</v>
+      </c>
+      <c r="E2">
+        <v>3.966691562352471</v>
+      </c>
+      <c r="F2">
+        <v>4.911425027522244</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>1.902041201857778</v>
+      </c>
+      <c r="C3">
+        <v>3.738475646939477</v>
+      </c>
+      <c r="D3">
+        <v>5.619362907588088</v>
+      </c>
+      <c r="E3">
+        <v>7.459363368881154</v>
+      </c>
+      <c r="F3">
+        <v>9.238491827692043</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>3.041647371167722</v>
+      </c>
+      <c r="C4">
+        <v>5.751151354819526</v>
+      </c>
+      <c r="D4">
+        <v>8.473774267115751</v>
+      </c>
+      <c r="E4">
+        <v>11.4926673085764</v>
+      </c>
+      <c r="F4">
+        <v>13.95724576305618</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>3.825104230078561</v>
+      </c>
+      <c r="C5">
+        <v>7.417531527927818</v>
+      </c>
+      <c r="D5">
+        <v>10.89510149895017</v>
+      </c>
+      <c r="E5">
+        <v>14.83670743233446</v>
+      </c>
+      <c r="F5" s="2">
+        <v>18.25260483191915</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1">
+        <v>20</v>
+      </c>
+      <c r="B6">
+        <v>0.009330903182415223</v>
+      </c>
+      <c r="C6">
+        <v>0.01264779466121421</v>
+      </c>
+      <c r="D6">
+        <v>0.01595377687389163</v>
+      </c>
+      <c r="E6">
+        <v>0.02001047146386979</v>
+      </c>
+      <c r="F6">
+        <v>0.02338946449867328</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1">
+        <v>24</v>
+      </c>
+      <c r="B7">
+        <v>0.01014882820832514</v>
+      </c>
+      <c r="C7">
+        <v>0.01371402901213225</v>
+      </c>
+      <c r="D7">
+        <v>0.01678309027293293</v>
+      </c>
+      <c r="E7">
+        <v>0.01980660748119924</v>
+      </c>
+      <c r="F7">
+        <v>0.02316900966124215</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1">
+        <v>28</v>
+      </c>
+      <c r="B8">
+        <v>0.01008961916104184</v>
+      </c>
+      <c r="C8">
+        <v>0.01348108826680312</v>
+      </c>
+      <c r="D8">
+        <v>0.01653844312613438</v>
+      </c>
+      <c r="E8">
+        <v>0.019030494681429</v>
+      </c>
+      <c r="F8">
+        <v>0.02251078684908445</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>0.0108634218660511</v>
+      </c>
+      <c r="C9">
+        <v>0.01410910707304374</v>
+      </c>
+      <c r="D9">
+        <v>0.01731091604533832</v>
+      </c>
+      <c r="E9">
+        <v>0.02154101288832072</v>
+      </c>
+      <c r="F9">
+        <v>0.02398648434081322</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1">
+        <v>36</v>
+      </c>
+      <c r="B10">
+        <v>0.00989193641523793</v>
+      </c>
+      <c r="C10">
+        <v>0.01262631249244423</v>
+      </c>
+      <c r="D10">
+        <v>0.01553961910210889</v>
+      </c>
+      <c r="E10">
+        <v>0.01852159100059334</v>
+      </c>
+      <c r="F10">
+        <v>0.02140066421485329</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>1.16097905300425</v>
+      </c>
+      <c r="C2">
+        <v>2.082219501960722</v>
+      </c>
+      <c r="D2">
+        <v>2.888516166557337</v>
+      </c>
+      <c r="E2">
+        <v>4.035506223680481</v>
+      </c>
+      <c r="F2">
+        <v>4.853496625719777</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>1.840252322131753</v>
+      </c>
+      <c r="C3">
+        <v>3.721913263858843</v>
+      </c>
+      <c r="D3">
+        <v>5.612980122598738</v>
+      </c>
+      <c r="E3">
+        <v>7.513125222563869</v>
+      </c>
+      <c r="F3">
+        <v>9.324549977437526</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>3.03772087829618</v>
+      </c>
+      <c r="C4">
+        <v>5.772882471360969</v>
+      </c>
+      <c r="D4">
+        <v>8.517280019358736</v>
+      </c>
+      <c r="E4">
+        <v>11.36590445049253</v>
+      </c>
+      <c r="F4">
+        <v>13.98217432309441</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>3.821332009394906</v>
+      </c>
+      <c r="C5">
+        <v>7.455732377796193</v>
+      </c>
+      <c r="D5">
+        <v>10.89265193437802</v>
+      </c>
+      <c r="E5">
+        <v>14.89416827767738</v>
+      </c>
+      <c r="F5" s="2">
+        <v>18.11078385567937</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1">
+        <v>20</v>
+      </c>
+      <c r="B6">
+        <v>0.009397652312699704</v>
+      </c>
+      <c r="C6">
+        <v>0.01259387799454265</v>
+      </c>
+      <c r="D6">
+        <v>0.01600618726792503</v>
+      </c>
+      <c r="E6">
+        <v>0.02000553006593745</v>
+      </c>
+      <c r="F6">
+        <v>0.02322335920373602</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1">
+        <v>24</v>
+      </c>
+      <c r="B7">
+        <v>0.01040548003084524</v>
+      </c>
+      <c r="C7">
+        <v>0.01358466434169283</v>
+      </c>
+      <c r="D7">
+        <v>0.01674192932532876</v>
+      </c>
+      <c r="E7">
+        <v>0.01970472760158546</v>
+      </c>
+      <c r="F7">
+        <v>0.02299864955909225</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1">
+        <v>28</v>
+      </c>
+      <c r="B8">
+        <v>0.01043263605432837</v>
+      </c>
+      <c r="C8">
+        <v>0.01348235009819212</v>
+      </c>
+      <c r="D8">
+        <v>0.01661501725334298</v>
+      </c>
+      <c r="E8">
+        <v>0.01915105642140853</v>
+      </c>
+      <c r="F8">
+        <v>0.02262501757894247</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>0.01090053258190127</v>
+      </c>
+      <c r="C9">
+        <v>0.01418269432384388</v>
+      </c>
+      <c r="D9">
+        <v>0.01729116843294821</v>
+      </c>
+      <c r="E9">
+        <v>0.0218225455687939</v>
+      </c>
+      <c r="F9">
+        <v>0.02393753138473262</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1">
+        <v>36</v>
+      </c>
+      <c r="B10">
+        <v>0.009874669699678781</v>
+      </c>
+      <c r="C10">
+        <v>0.01264619797178012</v>
+      </c>
+      <c r="D10">
+        <v>0.01554806286553386</v>
+      </c>
+      <c r="E10">
+        <v>0.01844536052708936</v>
+      </c>
+      <c r="F10">
+        <v>0.02140970507512095</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>1.27936651386306</v>
+      </c>
+      <c r="C2">
+        <v>2.074000412322713</v>
+      </c>
+      <c r="D2">
+        <v>2.941544234027592</v>
+      </c>
+      <c r="E2">
+        <v>3.956987156888568</v>
+      </c>
+      <c r="F2">
+        <v>4.824380659743112</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>1.893171880950109</v>
+      </c>
+      <c r="C3">
+        <v>3.724487256711307</v>
+      </c>
+      <c r="D3">
+        <v>5.617875108644469</v>
+      </c>
+      <c r="E3">
+        <v>7.538801144152782</v>
+      </c>
+      <c r="F3">
+        <v>8.739280548252529</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>3.187239818677275</v>
+      </c>
+      <c r="C4">
+        <v>5.609530812628456</v>
+      </c>
+      <c r="D4">
+        <v>8.607641068813152</v>
+      </c>
+      <c r="E4">
+        <v>11.4191140559384</v>
+      </c>
+      <c r="F4">
+        <v>11.83102649469423</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>3.714405585521224</v>
+      </c>
+      <c r="C5">
+        <v>7.437044917978777</v>
+      </c>
+      <c r="D5">
+        <v>10.94714941442138</v>
+      </c>
+      <c r="E5">
+        <v>14.50073955519642</v>
+      </c>
+      <c r="F5" s="2">
+        <v>16.27480019134302</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1">
+        <v>20</v>
+      </c>
+      <c r="B6">
+        <v>0.009404351689014634</v>
+      </c>
+      <c r="C6">
+        <v>0.012791228011948</v>
+      </c>
+      <c r="D6">
+        <v>0.01659254901500537</v>
+      </c>
+      <c r="E6">
+        <v>0.0200385490978063</v>
+      </c>
+      <c r="F6">
+        <v>0.02316152683468244</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1">
+        <v>24</v>
+      </c>
+      <c r="B7">
+        <v>0.01037177624439325</v>
+      </c>
+      <c r="C7">
+        <v>0.01358153146304558</v>
+      </c>
+      <c r="D7">
+        <v>0.01657416376722369</v>
+      </c>
+      <c r="E7">
+        <v>0.01984246200367792</v>
+      </c>
+      <c r="F7">
+        <v>0.0230230938411128</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1">
+        <v>28</v>
+      </c>
+      <c r="B8">
+        <v>0.01038352841562161</v>
+      </c>
+      <c r="C8">
+        <v>0.01325949263383141</v>
+      </c>
+      <c r="D8">
+        <v>0.01611718729649638</v>
+      </c>
+      <c r="E8">
+        <v>0.01904497146675652</v>
+      </c>
+      <c r="F8">
+        <v>0.02250792611266275</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>0.01098177495220728</v>
+      </c>
+      <c r="C9">
+        <v>0.01412848241398217</v>
+      </c>
+      <c r="D9">
+        <v>0.01741120836587159</v>
+      </c>
+      <c r="E9">
+        <v>0.02145646023681445</v>
+      </c>
+      <c r="F9">
+        <v>0.02402212286989389</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1">
+        <v>36</v>
+      </c>
+      <c r="B10">
+        <v>0.009819375812252756</v>
+      </c>
+      <c r="C10">
+        <v>0.0126144488976335</v>
+      </c>
+      <c r="D10">
+        <v>0.01555324566562046</v>
+      </c>
+      <c r="E10">
+        <v>0.01846562052332087</v>
+      </c>
+      <c r="F10">
+        <v>0.0214245858832523</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>1.355425566459662</v>
+      </c>
+      <c r="C2">
+        <v>1.896919712415062</v>
+      </c>
+      <c r="D2">
+        <v>3.06573992457644</v>
+      </c>
+      <c r="E2">
+        <v>3.980652111474568</v>
+      </c>
+      <c r="F2">
+        <v>4.676945789550945</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>1.970993335537137</v>
+      </c>
+      <c r="C3">
+        <v>3.802035365656062</v>
+      </c>
+      <c r="D3">
+        <v>5.636876597710175</v>
+      </c>
+      <c r="E3">
+        <v>7.562920812588094</v>
+      </c>
+      <c r="F3">
+        <v>7.380599543075505</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>3.280628368312117</v>
+      </c>
+      <c r="C4">
+        <v>5.819585646702822</v>
+      </c>
+      <c r="D4">
+        <v>8.616385696529674</v>
+      </c>
+      <c r="E4">
+        <v>11.5158824914428</v>
+      </c>
+      <c r="F4">
+        <v>11.07082758564438</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>4.089296666274949</v>
+      </c>
+      <c r="C5">
+        <v>7.564765243592343</v>
+      </c>
+      <c r="D5">
+        <v>11.18488897397342</v>
+      </c>
+      <c r="E5">
+        <v>14.60757761838626</v>
+      </c>
+      <c r="F5" s="2">
+        <v>14.89104558642253</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1">
+        <v>20</v>
+      </c>
+      <c r="B6">
+        <v>0.009406922217826763</v>
+      </c>
+      <c r="C6">
+        <v>0.01268799421911359</v>
+      </c>
+      <c r="D6">
+        <v>0.01674394774434331</v>
+      </c>
+      <c r="E6">
+        <v>0.02003169140548988</v>
+      </c>
+      <c r="F6">
+        <v>0.02330732095578533</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1">
+        <v>24</v>
+      </c>
+      <c r="B7">
+        <v>0.01031727211644048</v>
+      </c>
+      <c r="C7">
+        <v>0.0133719669810433</v>
+      </c>
+      <c r="D7">
+        <v>0.01668999807479309</v>
+      </c>
+      <c r="E7">
+        <v>0.01985007732558028</v>
+      </c>
+      <c r="F7">
+        <v>0.02311029526167263</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1">
+        <v>28</v>
+      </c>
+      <c r="B8">
+        <v>0.01026532524691093</v>
+      </c>
+      <c r="C8">
+        <v>0.01332858428743375</v>
+      </c>
+      <c r="D8">
+        <v>0.01602758328852267</v>
+      </c>
+      <c r="E8">
+        <v>0.01922695329831147</v>
+      </c>
+      <c r="F8">
+        <v>0.02243020953260181</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>0.01132221094620213</v>
+      </c>
+      <c r="C9">
+        <v>0.01421303552821464</v>
+      </c>
+      <c r="D9">
+        <v>0.01735594665486194</v>
+      </c>
+      <c r="E9">
+        <v>0.02143643465469742</v>
+      </c>
+      <c r="F9">
+        <v>0.02400803096390862</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1">
+        <v>36</v>
+      </c>
+      <c r="B10">
+        <v>0.009808166348122035</v>
+      </c>
+      <c r="C10">
+        <v>0.01262322270133826</v>
+      </c>
+      <c r="D10">
+        <v>0.01551101264032691</v>
+      </c>
+      <c r="E10">
+        <v>0.01847197701990151</v>
+      </c>
+      <c r="F10">
+        <v>0.02138974555477529</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>1.350072774735676</v>
+      </c>
+      <c r="C2">
+        <v>2.16897793048302</v>
+      </c>
+      <c r="D2">
+        <v>3.030855110635883</v>
+      </c>
+      <c r="E2">
+        <v>4.107873254704889</v>
+      </c>
+      <c r="F2">
+        <v>4.221542045666649</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>2.188206477151774</v>
+      </c>
+      <c r="C3">
+        <v>3.9730784965137</v>
+      </c>
+      <c r="D3">
+        <v>5.79711497588967</v>
+      </c>
+      <c r="E3">
+        <v>7.543074184311048</v>
+      </c>
+      <c r="F3">
+        <v>5.75193088019974</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>3.286623279692153</v>
+      </c>
+      <c r="C4">
+        <v>6.101129262515951</v>
+      </c>
+      <c r="D4">
+        <v>8.713641977562673</v>
+      </c>
+      <c r="E4">
+        <v>11.58676156145741</v>
+      </c>
+      <c r="F4">
+        <v>9.006376360048607</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>4.096301710888544</v>
+      </c>
+      <c r="C5">
+        <v>7.754478703149696</v>
+      </c>
+      <c r="D5">
+        <v>11.33126958009772</v>
+      </c>
+      <c r="E5" s="2">
+        <v>14.74359691154667</v>
+      </c>
+      <c r="F5">
+        <v>12.06749148080779</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1">
+        <v>20</v>
+      </c>
+      <c r="B6">
+        <v>0.009171972359911759</v>
+      </c>
+      <c r="C6">
+        <v>0.0127818693969554</v>
+      </c>
+      <c r="D6">
+        <v>0.0168199102102503</v>
+      </c>
+      <c r="E6">
+        <v>0.02009316829519867</v>
+      </c>
+      <c r="F6">
+        <v>0.02336585032525018</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1">
+        <v>24</v>
+      </c>
+      <c r="B7">
+        <v>0.0102300437138492</v>
+      </c>
+      <c r="C7">
+        <v>0.01347910483689552</v>
+      </c>
+      <c r="D7">
+        <v>0.01670093074728411</v>
+      </c>
+      <c r="E7">
+        <v>0.01987924547958056</v>
+      </c>
+      <c r="F7">
+        <v>0.02303815930720909</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1">
+        <v>28</v>
+      </c>
+      <c r="B8">
+        <v>0.01024147486349399</v>
+      </c>
+      <c r="C8">
+        <v>0.01321352385479444</v>
+      </c>
+      <c r="D8">
+        <v>0.01591238971864987</v>
+      </c>
+      <c r="E8">
+        <v>0.01901402229544778</v>
+      </c>
+      <c r="F8">
+        <v>0.02224125771320721</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>0.01135449337952468</v>
+      </c>
+      <c r="C9">
+        <v>0.01449392114643842</v>
+      </c>
+      <c r="D9">
+        <v>0.01739883969703886</v>
+      </c>
+      <c r="E9">
+        <v>0.02166904299090505</v>
+      </c>
+      <c r="F9">
+        <v>0.02406066917141898</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1">
+        <v>36</v>
+      </c>
+      <c r="B10">
+        <v>0.009945202599558386</v>
+      </c>
+      <c r="C10">
+        <v>0.01261107958147585</v>
+      </c>
+      <c r="D10">
+        <v>0.01552799974346109</v>
+      </c>
+      <c r="E10">
+        <v>0.01845668208249128</v>
+      </c>
+      <c r="F10">
+        <v>0.02141394941360544</v>
       </c>
     </row>
   </sheetData>
@@ -1039,11 +4214,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1063,7 +4238,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2" s="1">
         <v>4</v>
       </c>
@@ -1071,39 +4246,39 @@
         <v>1.168307897274945</v>
       </c>
       <c r="C2">
-        <v>1.9308557347346169</v>
+        <v>1.930855734734617</v>
       </c>
       <c r="D2">
-        <v>3.0449688135605091</v>
+        <v>3.044968813560509</v>
       </c>
       <c r="E2">
-        <v>3.8628145733736599</v>
+        <v>3.86281457337366</v>
       </c>
       <c r="F2">
-        <v>4.8509361363736536</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>4.850936136373654</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1">
         <v>8</v>
       </c>
       <c r="B3">
-        <v>2.0533945902780899</v>
+        <v>2.05339459027809</v>
       </c>
       <c r="C3">
-        <v>3.6398825814416589</v>
+        <v>3.639882581441659</v>
       </c>
       <c r="D3">
-        <v>5.6032836495775724</v>
+        <v>5.603283649577572</v>
       </c>
       <c r="E3">
-        <v>7.5354223011772206</v>
+        <v>7.535422301177221</v>
       </c>
       <c r="F3">
-        <v>9.4569090445053785</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>9.456909044505379</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1">
         <v>12</v>
       </c>
@@ -1111,7 +4286,7 @@
         <v>3.082435248453292</v>
       </c>
       <c r="C4">
-        <v>5.6282103632048814</v>
+        <v>5.628210363204881</v>
       </c>
       <c r="D4">
         <v>8.696548870731398</v>
@@ -1123,15 +4298,15 @@
         <v>14.45782037175268</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5" s="1">
         <v>16</v>
       </c>
       <c r="B5">
-        <v>4.2479699330955496</v>
+        <v>4.24796993309555</v>
       </c>
       <c r="C5">
-        <v>7.4104385796888863</v>
+        <v>7.410438579688886</v>
       </c>
       <c r="D5">
         <v>11.26726093586098</v>
@@ -1140,35 +4315,35 @@
         <v>15.01030387412413</v>
       </c>
       <c r="F5">
-        <v>18.847868072005369</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>18.84786807200537</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="1">
         <v>20</v>
       </c>
       <c r="B6">
-        <v>4.7549842868216556</v>
+        <v>4.754984286821656</v>
       </c>
       <c r="C6">
-        <v>9.0524638932760109</v>
+        <v>9.052463893276011</v>
       </c>
       <c r="D6">
         <v>13.88725941974632</v>
       </c>
       <c r="E6">
-        <v>18.381952622969209</v>
+        <v>18.38195262296921</v>
       </c>
       <c r="F6">
         <v>22.20133023400312</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7" s="1">
         <v>24</v>
       </c>
       <c r="B7">
-        <v>5.9930912983906053</v>
+        <v>5.993091298390605</v>
       </c>
       <c r="C7">
         <v>10.38266370327077</v>
@@ -1177,18 +4352,18 @@
         <v>16.30577776692909</v>
       </c>
       <c r="E7">
-        <v>21.850458503371549</v>
+        <v>21.85045850337155</v>
       </c>
       <c r="F7">
-        <v>26.994249302525478</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>26.99424930252548</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="1">
         <v>28</v>
       </c>
       <c r="B8">
-        <v>6.4280245446061572</v>
+        <v>6.428024544606157</v>
       </c>
       <c r="C8">
         <v>12.35940043721229</v>
@@ -1197,50 +4372,61 @@
         <v>19.01303186510296</v>
       </c>
       <c r="E8">
-        <v>25.063133080013749</v>
+        <v>25.06313308001375</v>
       </c>
       <c r="F8">
         <v>31.16978052458159</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6">
       <c r="A9" s="1">
         <v>32</v>
       </c>
       <c r="B9">
-        <v>7.8239127733386624</v>
+        <v>7.823912773338662</v>
       </c>
       <c r="C9">
-        <v>13.954988415735681</v>
+        <v>13.95498841573568</v>
       </c>
       <c r="D9">
-        <v>21.186822310529539</v>
+        <v>21.18682231052954</v>
       </c>
       <c r="E9">
         <v>28.26900392985138</v>
       </c>
       <c r="F9">
-        <v>35.186470999923529</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>35.18647099992353</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="1">
         <v>36</v>
       </c>
       <c r="B10">
-        <v>7.9711338912770673</v>
+        <v>7.971133891277067</v>
       </c>
       <c r="C10">
         <v>15.57953368448616</v>
       </c>
       <c r="D10">
-        <v>23.705319632255861</v>
+        <v>23.70531963225586</v>
       </c>
       <c r="E10">
-        <v>31.446767434248411</v>
-      </c>
-      <c r="F10" s="3">
-        <v>39.664947130344778</v>
+        <v>31.44676743424841</v>
+      </c>
+      <c r="F10">
+        <v>39.66494713034478</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1">
+        <v>40</v>
+      </c>
+      <c r="E11">
+        <v>34.44819355631628</v>
+      </c>
+      <c r="F11" s="2">
+        <v>42.85161389042247</v>
       </c>
     </row>
   </sheetData>
@@ -1249,11 +4435,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1273,107 +4459,107 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2" s="1">
         <v>4</v>
       </c>
       <c r="B2">
-        <v>1.1719896161337591</v>
+        <v>1.171989616133759</v>
       </c>
       <c r="C2">
         <v>1.969294274542468</v>
       </c>
       <c r="D2">
-        <v>3.0386113533450141</v>
+        <v>3.038611353345014</v>
       </c>
       <c r="E2">
-        <v>3.9296997407229388</v>
+        <v>3.929699740722939</v>
       </c>
       <c r="F2">
-        <v>4.9205223779554279</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>4.920522377955428</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1">
         <v>8</v>
       </c>
       <c r="B3">
-        <v>1.9359268119394699</v>
+        <v>1.93592681193947</v>
       </c>
       <c r="C3">
-        <v>3.7689885618577792</v>
+        <v>3.768988561857779</v>
       </c>
       <c r="D3">
-        <v>5.6678932374394249</v>
+        <v>5.667893237439425</v>
       </c>
       <c r="E3">
         <v>7.558543841774906</v>
       </c>
       <c r="F3">
-        <v>9.4648545868450711</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>9.464854586845071</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1">
         <v>12</v>
       </c>
       <c r="B4">
-        <v>3.0717326252728259</v>
+        <v>3.071732625272826</v>
       </c>
       <c r="C4">
-        <v>5.6682719347908694</v>
+        <v>5.668271934790869</v>
       </c>
       <c r="D4">
-        <v>8.7193517228811395</v>
+        <v>8.719351722881139</v>
       </c>
       <c r="E4">
         <v>11.57032662106892</v>
       </c>
       <c r="F4">
-        <v>14.532391559296141</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>14.53239155929614</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1">
         <v>16</v>
       </c>
       <c r="B5">
-        <v>4.0954875171049157</v>
+        <v>4.095487517104916</v>
       </c>
       <c r="C5">
-        <v>7.4617774824618808</v>
+        <v>7.461777482461881</v>
       </c>
       <c r="D5">
-        <v>11.352808369076479</v>
+        <v>11.35280836907648</v>
       </c>
       <c r="E5">
-        <v>15.176354168919261</v>
+        <v>15.17635416891926</v>
       </c>
       <c r="F5">
         <v>18.98117365238533</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6" s="1">
         <v>20</v>
       </c>
       <c r="B6">
-        <v>4.7576630042834367</v>
+        <v>4.757663004283437</v>
       </c>
       <c r="C6">
-        <v>9.1449806876252726</v>
+        <v>9.144980687625273</v>
       </c>
       <c r="D6">
-        <v>13.988630838780271</v>
+        <v>13.98863083878027</v>
       </c>
       <c r="E6">
-        <v>18.530432210245191</v>
+        <v>18.53043221024519</v>
       </c>
       <c r="F6">
-        <v>22.675693797166659</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>22.67569379716666</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="1">
         <v>24</v>
       </c>
@@ -1381,19 +4567,19 @@
         <v>5.558697214066914</v>
       </c>
       <c r="C7">
-        <v>10.397372711565851</v>
+        <v>10.39737271156585</v>
       </c>
       <c r="D7">
         <v>16.286252038255</v>
       </c>
       <c r="E7">
-        <v>21.867519652377919</v>
+        <v>21.86751965237792</v>
       </c>
       <c r="F7">
-        <v>27.076334845174092</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>27.07633484517409</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="1">
         <v>28</v>
       </c>
@@ -1401,10 +4587,10 @@
         <v>6.420860474952228</v>
       </c>
       <c r="C8">
-        <v>12.480756439395959</v>
+        <v>12.48075643939596</v>
       </c>
       <c r="D8">
-        <v>19.083508110913961</v>
+        <v>19.08350811091396</v>
       </c>
       <c r="E8">
         <v>25.16588987980554</v>
@@ -1413,44 +4599,55 @@
         <v>31.41240596702427</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6">
       <c r="A9" s="1">
         <v>32</v>
       </c>
       <c r="B9">
-        <v>7.2193663188059771</v>
+        <v>7.219366318805977</v>
       </c>
       <c r="C9">
         <v>14.1095767189756</v>
       </c>
       <c r="D9">
-        <v>21.278143613012681</v>
+        <v>21.27814361301268</v>
       </c>
       <c r="E9">
-        <v>28.276229423662421</v>
+        <v>28.27622942366242</v>
       </c>
       <c r="F9">
-        <v>35.401049079987139</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>35.40104907998714</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="1">
         <v>36</v>
       </c>
       <c r="B10">
-        <v>7.9730930454617894</v>
+        <v>7.973093045461789</v>
       </c>
       <c r="C10">
         <v>15.66238304570704</v>
       </c>
       <c r="D10">
-        <v>23.823447160427811</v>
+        <v>23.82344716042781</v>
       </c>
       <c r="E10">
         <v>31.5711406823971</v>
       </c>
-      <c r="F10" s="3">
-        <v>39.906250716808017</v>
+      <c r="F10">
+        <v>39.90625071680802</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1">
+        <v>40</v>
+      </c>
+      <c r="E11">
+        <v>34.11278993236836</v>
+      </c>
+      <c r="F11" s="2">
+        <v>43.15200931520176</v>
       </c>
     </row>
   </sheetData>
@@ -1459,11 +4656,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1483,7 +4680,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2" s="1">
         <v>4</v>
       </c>
@@ -1491,19 +4688,19 @@
         <v>1.154616727153928</v>
       </c>
       <c r="C2">
-        <v>2.0653326901507452</v>
+        <v>2.065332690150745</v>
       </c>
       <c r="D2">
-        <v>2.8779357841358828</v>
+        <v>2.877935784135883</v>
       </c>
       <c r="E2">
-        <v>3.9811226162802509</v>
+        <v>3.981122616280251</v>
       </c>
       <c r="F2">
-        <v>4.8417719316178562</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>4.841771931617856</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1">
         <v>8</v>
       </c>
@@ -1514,104 +4711,104 @@
         <v>3.720803084419277</v>
       </c>
       <c r="D3">
-        <v>5.6703831568408214</v>
+        <v>5.670383156840821</v>
       </c>
       <c r="E3">
-        <v>7.4671492956538819</v>
+        <v>7.467149295653882</v>
       </c>
       <c r="F3">
-        <v>9.4718528050042945</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>9.471852805004294</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1">
         <v>12</v>
       </c>
       <c r="B4">
-        <v>3.0423534555424632</v>
+        <v>3.042353455542463</v>
       </c>
       <c r="C4">
-        <v>5.8033435775180466</v>
+        <v>5.803343577518047</v>
       </c>
       <c r="D4">
         <v>8.588390885678324</v>
       </c>
       <c r="E4">
-        <v>11.526023821137031</v>
+        <v>11.52602382113703</v>
       </c>
       <c r="F4">
         <v>14.40288589977818</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5" s="1">
         <v>16</v>
       </c>
       <c r="B5">
-        <v>3.8334736531072759</v>
+        <v>3.833473653107276</v>
       </c>
       <c r="C5">
-        <v>7.4369394049607509</v>
+        <v>7.436939404960751</v>
       </c>
       <c r="D5">
-        <v>11.268865185060379</v>
+        <v>11.26886518506038</v>
       </c>
       <c r="E5">
-        <v>15.075977533123041</v>
+        <v>15.07597753312304</v>
       </c>
       <c r="F5">
         <v>18.79218022218458</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6" s="1">
         <v>20</v>
       </c>
       <c r="B6">
-        <v>4.7112444031772753</v>
+        <v>4.711244403177275</v>
       </c>
       <c r="C6">
-        <v>9.2976592383152923</v>
+        <v>9.297659238315292</v>
       </c>
       <c r="D6">
         <v>13.7658042946953</v>
       </c>
       <c r="E6">
-        <v>18.533275950698599</v>
+        <v>18.5332759506986</v>
       </c>
       <c r="F6">
-        <v>23.015924002965921</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>23.01592400296592</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="1">
         <v>24</v>
       </c>
       <c r="B7">
-        <v>5.4488246283598771</v>
+        <v>5.448824628359877</v>
       </c>
       <c r="C7">
-        <v>10.455043556238859</v>
+        <v>10.45504355623886</v>
       </c>
       <c r="D7">
-        <v>16.263992823299262</v>
+        <v>16.26399282329926</v>
       </c>
       <c r="E7">
-        <v>21.820153459420389</v>
+        <v>21.82015345942039</v>
       </c>
       <c r="F7">
-        <v>27.288882795614711</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>27.28888279561471</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="1">
         <v>28</v>
       </c>
       <c r="B8">
-        <v>6.3377866420679387</v>
+        <v>6.337786642067939</v>
       </c>
       <c r="C8">
-        <v>12.679078005969229</v>
+        <v>12.67907800596923</v>
       </c>
       <c r="D8">
         <v>18.75894462497137</v>
@@ -1620,47 +4817,58 @@
         <v>25.3201608673983</v>
       </c>
       <c r="F8">
-        <v>31.367699980800591</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>31.36769998080059</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="1">
         <v>32</v>
       </c>
       <c r="B9">
-        <v>7.0383239371070934</v>
+        <v>7.038323937107093</v>
       </c>
       <c r="C9">
         <v>14.1578518650308</v>
       </c>
       <c r="D9">
-        <v>21.013495655183629</v>
+        <v>21.01349565518363</v>
       </c>
       <c r="E9">
-        <v>28.032173188967079</v>
+        <v>28.03217318896708</v>
       </c>
       <c r="F9">
-        <v>35.550654630157197</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>35.5506546301572</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="1">
         <v>36</v>
       </c>
       <c r="B10">
-        <v>7.8396272745456423</v>
+        <v>7.839627274545642</v>
       </c>
       <c r="C10">
         <v>15.81217604032379</v>
       </c>
       <c r="D10">
-        <v>23.552307266540339</v>
+        <v>23.55230726654034</v>
       </c>
       <c r="E10">
-        <v>31.648825787883169</v>
-      </c>
-      <c r="F10" s="3">
-        <v>39.405203263064521</v>
+        <v>31.64882578788317</v>
+      </c>
+      <c r="F10">
+        <v>39.40520326306452</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1">
+        <v>40</v>
+      </c>
+      <c r="E11">
+        <v>34.21498891942253</v>
+      </c>
+      <c r="F11" s="2">
+        <v>43.27053009705956</v>
       </c>
     </row>
   </sheetData>
@@ -1669,11 +4877,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1693,27 +4901,27 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2" s="1">
         <v>4</v>
       </c>
       <c r="B2">
-        <v>1.1746284716188979</v>
+        <v>1.174628471618898</v>
       </c>
       <c r="C2">
-        <v>2.0532306581051021</v>
+        <v>2.053230658105102</v>
       </c>
       <c r="D2">
-        <v>2.9283381291199708</v>
+        <v>2.928338129119971</v>
       </c>
       <c r="E2">
-        <v>4.0360416821740968</v>
+        <v>4.036041682174097</v>
       </c>
       <c r="F2">
-        <v>4.8847593087993912</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>4.884759308799391</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1">
         <v>8</v>
       </c>
@@ -1724,44 +4932,44 @@
         <v>3.780493481461809</v>
       </c>
       <c r="D3">
-        <v>5.6905110713482197</v>
+        <v>5.69051107134822</v>
       </c>
       <c r="E3">
         <v>7.434656617617887</v>
       </c>
       <c r="F3">
-        <v>9.5636531817600687</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>9.563653181760069</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1">
         <v>12</v>
       </c>
       <c r="B4">
-        <v>3.0652145018577559</v>
+        <v>3.065214501857756</v>
       </c>
       <c r="C4">
-        <v>5.8017312127462581</v>
+        <v>5.801731212746258</v>
       </c>
       <c r="D4">
-        <v>8.6157534900361004</v>
+        <v>8.6157534900361</v>
       </c>
       <c r="E4">
-        <v>11.613576353660269</v>
+        <v>11.61357635366027</v>
       </c>
       <c r="F4">
         <v>14.5473561274967</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5" s="1">
         <v>16</v>
       </c>
       <c r="B5">
-        <v>3.7670549927078452</v>
+        <v>3.767054992707845</v>
       </c>
       <c r="C5">
-        <v>7.4892618368620409</v>
+        <v>7.489261836862041</v>
       </c>
       <c r="D5">
         <v>11.3543149742961</v>
@@ -1770,41 +4978,41 @@
         <v>15.17629970913792</v>
       </c>
       <c r="F5">
-        <v>18.986774058755991</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>18.98677405875599</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="1">
         <v>20</v>
       </c>
       <c r="B6">
-        <v>4.7426173335764288</v>
+        <v>4.742617333576429</v>
       </c>
       <c r="C6">
-        <v>9.3397884607101762</v>
+        <v>9.339788460710176</v>
       </c>
       <c r="D6">
         <v>13.87294443432158</v>
       </c>
       <c r="E6">
-        <v>18.655434251489378</v>
+        <v>18.65543425148938</v>
       </c>
       <c r="F6">
         <v>23.17005317086209</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7" s="1">
         <v>24</v>
       </c>
       <c r="B7">
-        <v>5.3921628882325594</v>
+        <v>5.392162888232559</v>
       </c>
       <c r="C7">
         <v>10.42705562098185</v>
       </c>
       <c r="D7">
-        <v>16.305864889542448</v>
+        <v>16.30586488954245</v>
       </c>
       <c r="E7">
         <v>21.85451427667623</v>
@@ -1813,47 +5021,47 @@
         <v>27.35303038794061</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8" s="1">
         <v>28</v>
       </c>
       <c r="B8">
-        <v>6.4038259687080599</v>
+        <v>6.40382596870806</v>
       </c>
       <c r="C8">
-        <v>12.686635633236699</v>
+        <v>12.6866356332367</v>
       </c>
       <c r="D8">
-        <v>18.829283973031881</v>
+        <v>18.82928397303188</v>
       </c>
       <c r="E8">
-        <v>25.396563324027529</v>
+        <v>25.39656332402753</v>
       </c>
       <c r="F8">
-        <v>31.505688723928859</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>31.50568872392886</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="1">
         <v>32</v>
       </c>
       <c r="B9">
-        <v>6.9749817362492452</v>
+        <v>6.974981736249245</v>
       </c>
       <c r="C9">
         <v>14.18797115483761</v>
       </c>
       <c r="D9">
-        <v>21.066089758631431</v>
+        <v>21.06608975863143</v>
       </c>
       <c r="E9">
-        <v>28.393896687503151</v>
+        <v>28.39389668750315</v>
       </c>
       <c r="F9">
-        <v>35.421843079106161</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>35.42184307910616</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="1">
         <v>36</v>
       </c>
@@ -1861,16 +5069,30 @@
         <v>7.96055244877601</v>
       </c>
       <c r="C10">
-        <v>15.851620183559451</v>
+        <v>15.85162018355945</v>
       </c>
       <c r="D10">
-        <v>23.656638783683679</v>
+        <v>23.65663878368368</v>
       </c>
       <c r="E10">
-        <v>31.824493984616922</v>
-      </c>
-      <c r="F10" s="3">
-        <v>39.533164671162673</v>
+        <v>31.82449398461692</v>
+      </c>
+      <c r="F10">
+        <v>39.53316467116267</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1">
+        <v>40</v>
+      </c>
+      <c r="D11">
+        <v>25.86974495773886</v>
+      </c>
+      <c r="E11">
+        <v>34.48118880304661</v>
+      </c>
+      <c r="F11" s="2">
+        <v>42.75022834210404</v>
       </c>
     </row>
   </sheetData>
@@ -1879,11 +5101,11 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1903,32 +5125,32 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2" s="1">
         <v>4</v>
       </c>
       <c r="B2">
-        <v>1.1610358570509569</v>
+        <v>1.161035857050957</v>
       </c>
       <c r="C2">
-        <v>1.9163703480360941</v>
+        <v>1.916370348036094</v>
       </c>
       <c r="D2">
-        <v>3.0356193058545671</v>
+        <v>3.035619305854567</v>
       </c>
       <c r="E2">
-        <v>3.9213030884246489</v>
+        <v>3.921303088424649</v>
       </c>
       <c r="F2">
         <v>4.936125471420346</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3" s="1">
         <v>8</v>
       </c>
       <c r="B3">
-        <v>1.9237700835138041</v>
+        <v>1.923770083513804</v>
       </c>
       <c r="C3">
         <v>3.727450509696336</v>
@@ -1937,33 +5159,33 @@
         <v>5.677477653504293</v>
       </c>
       <c r="E3">
-        <v>7.4339248548206314</v>
+        <v>7.433924854820631</v>
       </c>
       <c r="F3">
-        <v>9.4561416961633995</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>9.4561416961634</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1">
         <v>12</v>
       </c>
       <c r="B4">
-        <v>3.0614167529405529</v>
+        <v>3.061416752940553</v>
       </c>
       <c r="C4">
-        <v>5.6183224282569197</v>
+        <v>5.61832242825692</v>
       </c>
       <c r="D4">
-        <v>8.6450054148960067</v>
+        <v>8.645005414896007</v>
       </c>
       <c r="E4">
         <v>11.53510640892673</v>
       </c>
       <c r="F4">
-        <v>14.473083303797219</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>14.47308330379722</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1">
         <v>16</v>
       </c>
@@ -1971,10 +5193,10 @@
         <v>3.75369682490249</v>
       </c>
       <c r="C5">
-        <v>7.4471130378767869</v>
+        <v>7.447113037876787</v>
       </c>
       <c r="D5">
-        <v>11.291040527750461</v>
+        <v>11.29104052775046</v>
       </c>
       <c r="E5">
         <v>15.0286265868407</v>
@@ -1983,27 +5205,27 @@
         <v>18.79675173096199</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6" s="1">
         <v>20</v>
       </c>
       <c r="B6">
-        <v>4.7393194125424509</v>
+        <v>4.739319412542451</v>
       </c>
       <c r="C6">
-        <v>9.1308421871200025</v>
+        <v>9.130842187120003</v>
       </c>
       <c r="D6">
         <v>13.87089848104563</v>
       </c>
       <c r="E6">
-        <v>18.402673887570149</v>
+        <v>18.40267388757015</v>
       </c>
       <c r="F6">
-        <v>23.143467843483009</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>23.14346784348301</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="1">
         <v>24</v>
       </c>
@@ -2014,36 +5236,36 @@
         <v>10.4024055434957</v>
       </c>
       <c r="D7">
-        <v>16.329056992670878</v>
+        <v>16.32905699267088</v>
       </c>
       <c r="E7">
-        <v>21.862238326818481</v>
+        <v>21.86223832681848</v>
       </c>
       <c r="F7">
-        <v>26.971727989002162</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>26.97172798900216</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="1">
         <v>28</v>
       </c>
       <c r="B8">
-        <v>6.4030644185827983</v>
+        <v>6.403064418582798</v>
       </c>
       <c r="C8">
         <v>12.42650462960512</v>
       </c>
       <c r="D8">
-        <v>18.979936375643341</v>
+        <v>18.97993637564334</v>
       </c>
       <c r="E8">
-        <v>24.328244853685721</v>
+        <v>24.32824485368572</v>
       </c>
       <c r="F8">
-        <v>31.660456881834389</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>31.66045688183439</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="1">
         <v>32</v>
       </c>
@@ -2051,36 +5273,50 @@
         <v>6.992161735848037</v>
       </c>
       <c r="C9">
-        <v>14.212425741683679</v>
+        <v>14.21242574168368</v>
       </c>
       <c r="D9">
-        <v>19.747378481221709</v>
+        <v>19.74737848122171</v>
       </c>
       <c r="E9">
-        <v>28.464116841829121</v>
+        <v>28.46411684182912</v>
       </c>
       <c r="F9">
         <v>35.06143557205835</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6">
       <c r="A10" s="1">
         <v>36</v>
       </c>
       <c r="B10">
-        <v>7.9493878222356829</v>
+        <v>7.949387822235683</v>
       </c>
       <c r="C10">
         <v>15.64822618016775</v>
       </c>
       <c r="D10">
-        <v>23.701915115778242</v>
+        <v>23.70191511577824</v>
       </c>
       <c r="E10">
-        <v>31.519575064640112</v>
-      </c>
-      <c r="F10" s="3">
-        <v>38.863410399804607</v>
+        <v>31.51957506464011</v>
+      </c>
+      <c r="F10">
+        <v>38.86341039980461</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1">
+        <v>40</v>
+      </c>
+      <c r="D11">
+        <v>25.73666082275691</v>
+      </c>
+      <c r="E11">
+        <v>34.59810290378981</v>
+      </c>
+      <c r="F11" s="2">
+        <v>42.8314549908524</v>
       </c>
     </row>
   </sheetData>
@@ -2089,11 +5325,11 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2113,67 +5349,67 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2" s="1">
         <v>4</v>
       </c>
       <c r="B2">
-        <v>1.1495720994639069</v>
+        <v>1.149572099463907</v>
       </c>
       <c r="C2">
-        <v>1.9651277199501029</v>
+        <v>1.965127719950103</v>
       </c>
       <c r="D2">
         <v>3.04927052115498</v>
       </c>
       <c r="E2">
-        <v>3.9219088960403532</v>
+        <v>3.921908896040353</v>
       </c>
       <c r="F2">
-        <v>4.9921802559320332</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>4.992180255932033</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1">
         <v>8</v>
       </c>
       <c r="B3">
-        <v>1.9638791213768361</v>
+        <v>1.963879121376836</v>
       </c>
       <c r="C3">
-        <v>3.7999230867462912</v>
+        <v>3.799923086746291</v>
       </c>
       <c r="D3">
-        <v>5.6882576827653724</v>
+        <v>5.688257682765372</v>
       </c>
       <c r="E3">
-        <v>7.6143992138641172</v>
+        <v>7.614399213864117</v>
       </c>
       <c r="F3">
-        <v>8.9564941550719297</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>8.95649415507193</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1">
         <v>12</v>
       </c>
       <c r="B4">
-        <v>3.0583123684118898</v>
+        <v>3.05831236841189</v>
       </c>
       <c r="C4">
-        <v>5.6820948331825951</v>
+        <v>5.682094833182595</v>
       </c>
       <c r="D4">
-        <v>8.7335875795053397</v>
+        <v>8.73358757950534</v>
       </c>
       <c r="E4">
-        <v>11.595902260806801</v>
+        <v>11.5959022608068</v>
       </c>
       <c r="F4">
-        <v>14.484841623163501</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>14.4848416231635</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1">
         <v>16</v>
       </c>
@@ -2181,116 +5417,130 @@
         <v>3.77458526717946</v>
       </c>
       <c r="C5">
-        <v>7.4992673362781774</v>
+        <v>7.499267336278177</v>
       </c>
       <c r="D5">
-        <v>11.373064509459549</v>
+        <v>11.37306450945955</v>
       </c>
       <c r="E5">
-        <v>15.186133048134989</v>
+        <v>15.18613304813499</v>
       </c>
       <c r="F5">
         <v>18.42490365234616</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6" s="1">
         <v>20</v>
       </c>
       <c r="B6">
-        <v>4.7310471453365208</v>
+        <v>4.731047145336521</v>
       </c>
       <c r="C6">
-        <v>9.1980802985913321</v>
+        <v>9.198080298591332</v>
       </c>
       <c r="D6">
         <v>13.99512495646605</v>
       </c>
       <c r="E6">
-        <v>18.482688184778141</v>
+        <v>18.48268818477814</v>
       </c>
       <c r="F6">
-        <v>22.623858837102009</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>22.62385883710201</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="1">
         <v>24</v>
       </c>
       <c r="B7">
-        <v>5.5297196978936984</v>
+        <v>5.529719697893698</v>
       </c>
       <c r="C7">
         <v>10.7386324712133</v>
       </c>
       <c r="D7">
-        <v>16.295236434615081</v>
+        <v>16.29523643461508</v>
       </c>
       <c r="E7">
-        <v>21.885233838604041</v>
+        <v>21.88523383860404</v>
       </c>
       <c r="F7">
-        <v>27.032468764163461</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>27.03246876416346</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="1">
         <v>28</v>
       </c>
       <c r="B8">
-        <v>6.4006453317155083</v>
+        <v>6.400645331715508</v>
       </c>
       <c r="C8">
-        <v>12.509594375408691</v>
+        <v>12.50959437540869</v>
       </c>
       <c r="D8">
         <v>19.06145020801592</v>
       </c>
       <c r="E8">
-        <v>24.431815308614649</v>
+        <v>24.43181530861465</v>
       </c>
       <c r="F8">
-        <v>31.149984348452382</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>31.14998434845238</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="1">
         <v>32</v>
       </c>
       <c r="B9">
-        <v>7.0546406570947378</v>
+        <v>7.054640657094738</v>
       </c>
       <c r="C9">
         <v>14.22948922080362</v>
       </c>
       <c r="D9">
-        <v>19.510672550365339</v>
+        <v>19.51067255036534</v>
       </c>
       <c r="E9">
-        <v>28.430359769267429</v>
+        <v>28.43035976926743</v>
       </c>
       <c r="F9">
-        <v>35.171677038515917</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>35.17167703851592</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="1">
         <v>36</v>
       </c>
       <c r="B10">
-        <v>7.9523409269596499</v>
+        <v>7.95234092695965</v>
       </c>
       <c r="C10">
-        <v>15.715183820115669</v>
+        <v>15.71518382011567</v>
       </c>
       <c r="D10">
-        <v>23.808531039621059</v>
+        <v>23.80853103962106</v>
       </c>
       <c r="E10">
-        <v>31.622595575768599</v>
-      </c>
-      <c r="F10" s="3">
-        <v>39.036547770194289</v>
+        <v>31.6225955757686</v>
+      </c>
+      <c r="F10">
+        <v>39.03654777019429</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1">
+        <v>40</v>
+      </c>
+      <c r="D11">
+        <v>25.8325192452845</v>
+      </c>
+      <c r="E11">
+        <v>34.23774365552017</v>
+      </c>
+      <c r="F11" s="2">
+        <v>42.76695032462215</v>
       </c>
     </row>
   </sheetData>
@@ -2299,11 +5549,11 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2323,12 +5573,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2" s="1">
         <v>4</v>
       </c>
       <c r="B2">
-        <v>1.3074195961698529</v>
+        <v>1.307419596169853</v>
       </c>
       <c r="C2">
         <v>2.14473005108281</v>
@@ -2337,44 +5587,44 @@
         <v>2.976309948195341</v>
       </c>
       <c r="E2">
-        <v>4.0795668473492261</v>
+        <v>4.079566847349226</v>
       </c>
       <c r="F2">
-        <v>4.7455203672027553</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>4.745520367202755</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1">
         <v>8</v>
       </c>
       <c r="B3">
-        <v>2.0082376097908461</v>
+        <v>2.008237609790846</v>
       </c>
       <c r="C3">
         <v>3.858431988094432</v>
       </c>
       <c r="D3">
-        <v>5.7936990633046577</v>
+        <v>5.793699063304658</v>
       </c>
       <c r="E3">
-        <v>7.6053435502187741</v>
+        <v>7.605343550218774</v>
       </c>
       <c r="F3">
-        <v>7.4129448991815634</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>7.412944899181563</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1">
         <v>12</v>
       </c>
       <c r="B4">
-        <v>3.2698619217197549</v>
+        <v>3.269861921719755</v>
       </c>
       <c r="C4">
-        <v>5.9378678840520331</v>
+        <v>5.937867884052033</v>
       </c>
       <c r="D4">
-        <v>8.8018117370689861</v>
+        <v>8.801811737068986</v>
       </c>
       <c r="E4">
         <v>11.64683859389598</v>
@@ -2383,58 +5633,58 @@
         <v>13.13028261040345</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5" s="1">
         <v>16</v>
       </c>
       <c r="B5">
-        <v>3.8480375838258549</v>
+        <v>3.848037583825855</v>
       </c>
       <c r="C5">
-        <v>7.6633625348809433</v>
+        <v>7.663362534880943</v>
       </c>
       <c r="D5">
         <v>11.39976993781619</v>
       </c>
       <c r="E5">
-        <v>15.214981065683711</v>
+        <v>15.21498106568371</v>
       </c>
       <c r="F5">
         <v>14.73903929631542</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6" s="1">
         <v>20</v>
       </c>
       <c r="B6">
-        <v>5.0942080394129396</v>
+        <v>5.09420803941294</v>
       </c>
       <c r="C6">
-        <v>9.4237447146210016</v>
+        <v>9.423744714621002</v>
       </c>
       <c r="D6">
         <v>13.97023680123141</v>
       </c>
       <c r="E6">
-        <v>18.545272943128431</v>
+        <v>18.54527294312843</v>
       </c>
       <c r="F6">
-        <v>21.494371909400162</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>21.49437190940016</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="1">
         <v>24</v>
       </c>
       <c r="B7">
-        <v>5.5548691028619581</v>
+        <v>5.554869102861958</v>
       </c>
       <c r="C7">
         <v>10.97310925876665</v>
       </c>
       <c r="D7">
-        <v>16.421470825011639</v>
+        <v>16.42147082501164</v>
       </c>
       <c r="E7">
         <v>21.75608826061255</v>
@@ -2443,27 +5693,27 @@
         <v>27.06622367286408</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8" s="1">
         <v>28</v>
       </c>
       <c r="B8">
-        <v>6.5872228778853597</v>
+        <v>6.58722287788536</v>
       </c>
       <c r="C8">
         <v>12.87288716023887</v>
       </c>
       <c r="D8">
-        <v>18.965943681187909</v>
+        <v>18.96594368118791</v>
       </c>
       <c r="E8">
-        <v>24.682360109406559</v>
+        <v>24.68236010940656</v>
       </c>
       <c r="F8">
-        <v>30.029901166477568</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>30.02990116647757</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="1">
         <v>32</v>
       </c>
@@ -2471,36 +5721,50 @@
         <v>7.384262201923562</v>
       </c>
       <c r="C9">
-        <v>14.252878859540321</v>
+        <v>14.25287885954032</v>
       </c>
       <c r="D9">
-        <v>9.1788862399246227</v>
+        <v>9.178886239924623</v>
       </c>
       <c r="E9">
-        <v>28.237827834433151</v>
+        <v>28.23782783443315</v>
       </c>
       <c r="F9">
-        <v>31.722887238001089</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>31.72288723800109</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="1">
         <v>36</v>
       </c>
       <c r="B10">
-        <v>8.1121295927622068</v>
+        <v>8.112129592762207</v>
       </c>
       <c r="C10">
         <v>15.98556305913695</v>
       </c>
       <c r="D10">
-        <v>23.750361098146541</v>
+        <v>23.75036109814654</v>
       </c>
       <c r="E10">
-        <v>31.819849036100859</v>
+        <v>31.81984903610086</v>
       </c>
       <c r="F10" s="2">
-        <v>39.122531684429923</v>
+        <v>39.12253168442992</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1">
+        <v>40</v>
+      </c>
+      <c r="D11">
+        <v>25.87069186023036</v>
+      </c>
+      <c r="E11">
+        <v>34.40158886160417</v>
+      </c>
+      <c r="F11">
+        <v>38.50760781402564</v>
       </c>
     </row>
   </sheetData>
